--- a/research/traditional_assets/database/data/kenya/kenya_building_materials.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_building_materials.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1778362681190207</v>
+        <v>0.1773342593146636</v>
       </c>
       <c r="C2">
-        <v>0.8941115963580253</v>
+        <v>0.8854091512504496</v>
       </c>
       <c r="D2">
-        <v>0.3251115963580253</v>
+        <v>0.3253491512504496</v>
       </c>
       <c r="E2">
-        <v>-0.03</v>
+        <v>-0.02106</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.00894</v>
       </c>
       <c r="G2">
         <v>0.569</v>
@@ -1433,28 +1433,28 @@
         <v>0.397</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.000449682</v>
       </c>
       <c r="N2">
-        <v>0.397</v>
+        <v>0.396550318</v>
       </c>
       <c r="O2">
-        <v>0.1191</v>
+        <v>0.1189650954</v>
       </c>
       <c r="P2">
-        <v>0.2779</v>
+        <v>0.2775852226</v>
       </c>
       <c r="Q2">
-        <v>0.4559</v>
+        <v>0.4555852226</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1778362681190207</v>
+        <v>0.1787698578935996</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9271246956891773</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>882.8461001329829</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1773342593146636</v>
+        <v>0.1768322505103066</v>
       </c>
       <c r="C3">
-        <v>0.8854091512504496</v>
+        <v>0.8767070535533757</v>
       </c>
       <c r="D3">
-        <v>0.3253491512504496</v>
+        <v>0.3255870535533758</v>
       </c>
       <c r="E3">
-        <v>-0.02106</v>
+        <v>-0.01212</v>
       </c>
       <c r="F3">
-        <v>0.00894</v>
+        <v>0.01788</v>
       </c>
       <c r="G3">
         <v>0.569</v>
@@ -1515,28 +1515,28 @@
         <v>0.397</v>
       </c>
       <c r="M3">
-        <v>0.000449682</v>
+        <v>0.0008993639999999999</v>
       </c>
       <c r="N3">
-        <v>0.396550318</v>
+        <v>0.396100636</v>
       </c>
       <c r="O3">
-        <v>0.1189650954</v>
+        <v>0.1188301908</v>
       </c>
       <c r="P3">
-        <v>0.2775852226</v>
+        <v>0.2772704452</v>
       </c>
       <c r="Q3">
-        <v>0.4555852226</v>
+        <v>0.4552704452</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1787698578935996</v>
+        <v>0.179722500520721</v>
       </c>
       <c r="T3">
-        <v>0.9271246956891773</v>
+        <v>0.9337669416820787</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>882.8461001329829</v>
+        <v>441.4230500664914</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1768322505103066</v>
+        <v>0.1763302417059495</v>
       </c>
       <c r="C4">
-        <v>0.8767070535533757</v>
+        <v>0.8680053040294639</v>
       </c>
       <c r="D4">
-        <v>0.3255870535533758</v>
+        <v>0.3258253040294639</v>
       </c>
       <c r="E4">
-        <v>-0.01212</v>
+        <v>-0.003180000000000002</v>
       </c>
       <c r="F4">
-        <v>0.01788</v>
+        <v>0.02682</v>
       </c>
       <c r="G4">
         <v>0.569</v>
@@ -1597,28 +1597,28 @@
         <v>0.397</v>
       </c>
       <c r="M4">
-        <v>0.0008993639999999999</v>
+        <v>0.001349046</v>
       </c>
       <c r="N4">
-        <v>0.396100636</v>
+        <v>0.3956509539999999</v>
       </c>
       <c r="O4">
-        <v>0.1188301908</v>
+        <v>0.1186952862</v>
       </c>
       <c r="P4">
-        <v>0.2772704452</v>
+        <v>0.2769556678</v>
       </c>
       <c r="Q4">
-        <v>0.4552704452</v>
+        <v>0.4549556678</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.179722500520721</v>
+        <v>0.1806947852638655</v>
       </c>
       <c r="T4">
-        <v>0.9337669416820787</v>
+        <v>0.940546141200607</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>441.4230500664914</v>
+        <v>294.2820333776609</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1763302417059495</v>
+        <v>0.1758282329015924</v>
       </c>
       <c r="C5">
-        <v>0.8680053040294639</v>
+        <v>0.8593039034436074</v>
       </c>
       <c r="D5">
-        <v>0.3258253040294639</v>
+        <v>0.3260639034436075</v>
       </c>
       <c r="E5">
-        <v>-0.003180000000000002</v>
+        <v>0.005759999999999998</v>
       </c>
       <c r="F5">
-        <v>0.02682</v>
+        <v>0.03576</v>
       </c>
       <c r="G5">
         <v>0.569</v>
@@ -1679,28 +1679,28 @@
         <v>0.397</v>
       </c>
       <c r="M5">
-        <v>0.001349046</v>
+        <v>0.001798728</v>
       </c>
       <c r="N5">
-        <v>0.3956509539999999</v>
+        <v>0.3952012719999999</v>
       </c>
       <c r="O5">
-        <v>0.1186952862</v>
+        <v>0.1185603816</v>
       </c>
       <c r="P5">
-        <v>0.2769556678</v>
+        <v>0.2766408904</v>
       </c>
       <c r="Q5">
-        <v>0.4549556678</v>
+        <v>0.4546408903999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1806947852638655</v>
+        <v>0.1816873259391588</v>
       </c>
       <c r="T5">
-        <v>0.940546141200607</v>
+        <v>0.9474665740424378</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>294.2820333776609</v>
+        <v>220.7115250332457</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1758282329015924</v>
+        <v>0.1753262240972354</v>
       </c>
       <c r="C6">
-        <v>0.8593039034436074</v>
+        <v>0.8506028525629423</v>
       </c>
       <c r="D6">
-        <v>0.3260639034436075</v>
+        <v>0.3263028525629424</v>
       </c>
       <c r="E6">
-        <v>0.005759999999999998</v>
+        <v>0.0147</v>
       </c>
       <c r="F6">
-        <v>0.03576</v>
+        <v>0.0447</v>
       </c>
       <c r="G6">
         <v>0.569</v>
@@ -1761,28 +1761,28 @@
         <v>0.397</v>
       </c>
       <c r="M6">
-        <v>0.001798728</v>
+        <v>0.00224841</v>
       </c>
       <c r="N6">
-        <v>0.3952012719999999</v>
+        <v>0.39475159</v>
       </c>
       <c r="O6">
-        <v>0.1185603816</v>
+        <v>0.118425477</v>
       </c>
       <c r="P6">
-        <v>0.2766408904</v>
+        <v>0.276326113</v>
       </c>
       <c r="Q6">
-        <v>0.4546408903999999</v>
+        <v>0.454326113</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1816873259391588</v>
+        <v>0.1827007622076162</v>
       </c>
       <c r="T6">
-        <v>0.9474665740424378</v>
+        <v>0.9545327002072547</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>220.7115250332457</v>
+        <v>176.5692200265966</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1753262240972354</v>
+        <v>0.1748242152928783</v>
       </c>
       <c r="C7">
-        <v>0.8506028525629423</v>
+        <v>0.841902152156855</v>
       </c>
       <c r="D7">
-        <v>0.3263028525629424</v>
+        <v>0.3265421521568551</v>
       </c>
       <c r="E7">
-        <v>0.0147</v>
+        <v>0.02364</v>
       </c>
       <c r="F7">
-        <v>0.0447</v>
+        <v>0.05364000000000001</v>
       </c>
       <c r="G7">
         <v>0.569</v>
@@ -1843,28 +1843,28 @@
         <v>0.397</v>
       </c>
       <c r="M7">
-        <v>0.00224841</v>
+        <v>0.002698092</v>
       </c>
       <c r="N7">
-        <v>0.39475159</v>
+        <v>0.394301908</v>
       </c>
       <c r="O7">
-        <v>0.118425477</v>
+        <v>0.1182905724</v>
       </c>
       <c r="P7">
-        <v>0.276326113</v>
+        <v>0.2760113356</v>
       </c>
       <c r="Q7">
-        <v>0.454326113</v>
+        <v>0.4540113356</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1827007622076162</v>
+        <v>0.1837357609498705</v>
       </c>
       <c r="T7">
-        <v>0.9545327002072547</v>
+        <v>0.9617491694819612</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>176.5692200265966</v>
+        <v>147.1410166888305</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1748242152928783</v>
+        <v>0.1743222064885213</v>
       </c>
       <c r="C8">
-        <v>0.841902152156855</v>
+        <v>0.8332018029969902</v>
       </c>
       <c r="D8">
-        <v>0.3265421521568551</v>
+        <v>0.3267818029969902</v>
       </c>
       <c r="E8">
-        <v>0.02364</v>
+        <v>0.03258</v>
       </c>
       <c r="F8">
-        <v>0.05364</v>
+        <v>0.06258</v>
       </c>
       <c r="G8">
         <v>0.569</v>
@@ -1925,28 +1925,28 @@
         <v>0.397</v>
       </c>
       <c r="M8">
-        <v>0.002698092</v>
+        <v>0.003147774</v>
       </c>
       <c r="N8">
-        <v>0.394301908</v>
+        <v>0.393852226</v>
       </c>
       <c r="O8">
-        <v>0.1182905724</v>
+        <v>0.1181556678</v>
       </c>
       <c r="P8">
-        <v>0.2760113356</v>
+        <v>0.2756965582</v>
       </c>
       <c r="Q8">
-        <v>0.4540113356</v>
+        <v>0.4536965582</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1837357609498705</v>
+        <v>0.1847930177295928</v>
       </c>
       <c r="T8">
-        <v>0.9617491694819612</v>
+        <v>0.969120831644296</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>147.1410166888305</v>
+        <v>126.120871447569</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1743222064885213</v>
+        <v>0.1738201976841642</v>
       </c>
       <c r="C9">
-        <v>0.8332018029969902</v>
+        <v>0.8245018058572597</v>
       </c>
       <c r="D9">
-        <v>0.3267818029969903</v>
+        <v>0.3270218058572598</v>
       </c>
       <c r="E9">
-        <v>0.03258000000000001</v>
+        <v>0.04152</v>
       </c>
       <c r="F9">
-        <v>0.06258000000000001</v>
+        <v>0.07152</v>
       </c>
       <c r="G9">
         <v>0.569</v>
@@ -2007,28 +2007,28 @@
         <v>0.397</v>
       </c>
       <c r="M9">
-        <v>0.003147774</v>
+        <v>0.003597456</v>
       </c>
       <c r="N9">
-        <v>0.393852226</v>
+        <v>0.393402544</v>
       </c>
       <c r="O9">
-        <v>0.1181556678</v>
+        <v>0.1180207632</v>
       </c>
       <c r="P9">
-        <v>0.2756965582</v>
+        <v>0.2753817808</v>
       </c>
       <c r="Q9">
-        <v>0.4536965582</v>
+        <v>0.4533817808</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1847930177295928</v>
+        <v>0.1858732583523524</v>
       </c>
       <c r="T9">
-        <v>0.969120831644296</v>
+        <v>0.9766527473318988</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>126.120871447569</v>
+        <v>110.3557625166229</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1738201976841642</v>
+        <v>0.1733181888798071</v>
       </c>
       <c r="C10">
-        <v>0.8245018058572597</v>
+        <v>0.8158021615138508</v>
       </c>
       <c r="D10">
-        <v>0.3270218058572598</v>
+        <v>0.3272621615138508</v>
       </c>
       <c r="E10">
-        <v>0.04152</v>
+        <v>0.05046</v>
       </c>
       <c r="F10">
-        <v>0.07152</v>
+        <v>0.08046</v>
       </c>
       <c r="G10">
         <v>0.569</v>
@@ -2089,28 +2089,28 @@
         <v>0.397</v>
       </c>
       <c r="M10">
-        <v>0.003597456</v>
+        <v>0.004047138</v>
       </c>
       <c r="N10">
-        <v>0.393402544</v>
+        <v>0.392952862</v>
       </c>
       <c r="O10">
-        <v>0.1180207632</v>
+        <v>0.1178858586</v>
       </c>
       <c r="P10">
-        <v>0.2753817808</v>
+        <v>0.2750670034</v>
       </c>
       <c r="Q10">
-        <v>0.4533817808</v>
+        <v>0.4530670034</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1858732583523524</v>
+        <v>0.1869772405272606</v>
       </c>
       <c r="T10">
-        <v>0.9766527473318988</v>
+        <v>0.9843501996280202</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>110.3557625166229</v>
+        <v>98.09401112588698</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1733181888798071</v>
+        <v>0.1728161800754501</v>
       </c>
       <c r="C11">
-        <v>0.8158021615138508</v>
+        <v>0.8071028707452337</v>
       </c>
       <c r="D11">
-        <v>0.3272621615138508</v>
+        <v>0.3275028707452338</v>
       </c>
       <c r="E11">
-        <v>0.05046</v>
+        <v>0.05939999999999999</v>
       </c>
       <c r="F11">
-        <v>0.08046</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G11">
         <v>0.569</v>
@@ -2171,28 +2171,28 @@
         <v>0.397</v>
       </c>
       <c r="M11">
-        <v>0.004047138</v>
+        <v>0.004496819999999999</v>
       </c>
       <c r="N11">
-        <v>0.392952862</v>
+        <v>0.39250318</v>
       </c>
       <c r="O11">
-        <v>0.1178858586</v>
+        <v>0.117750954</v>
       </c>
       <c r="P11">
-        <v>0.2750670034</v>
+        <v>0.274752226</v>
       </c>
       <c r="Q11">
-        <v>0.4530670034</v>
+        <v>0.452752226</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1869772405272606</v>
+        <v>0.188105755639389</v>
       </c>
       <c r="T11">
-        <v>0.9843501996280202</v>
+        <v>0.9922187064196111</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>98.09401112588698</v>
+        <v>88.28461001329829</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1728161800754501</v>
+        <v>0.172314171271093</v>
       </c>
       <c r="C12">
-        <v>0.8071028707452337</v>
+        <v>0.7984039343321716</v>
       </c>
       <c r="D12">
-        <v>0.3275028707452338</v>
+        <v>0.3277439343321716</v>
       </c>
       <c r="E12">
-        <v>0.05940000000000001</v>
+        <v>0.06834</v>
       </c>
       <c r="F12">
-        <v>0.08940000000000001</v>
+        <v>0.09834</v>
       </c>
       <c r="G12">
         <v>0.569</v>
@@ -2253,28 +2253,28 @@
         <v>0.397</v>
       </c>
       <c r="M12">
-        <v>0.00449682</v>
+        <v>0.004946501999999999</v>
       </c>
       <c r="N12">
-        <v>0.39250318</v>
+        <v>0.3920534979999999</v>
       </c>
       <c r="O12">
-        <v>0.117750954</v>
+        <v>0.1176160494</v>
       </c>
       <c r="P12">
-        <v>0.274752226</v>
+        <v>0.2744374486</v>
       </c>
       <c r="Q12">
-        <v>0.452752226</v>
+        <v>0.4524374486</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.188105755639389</v>
+        <v>0.1892596306416776</v>
       </c>
       <c r="T12">
-        <v>0.9922187064196111</v>
+        <v>1.000264033588541</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>88.28461001329826</v>
+        <v>80.25873637572572</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.172314171271093</v>
+        <v>0.171812162466736</v>
       </c>
       <c r="C13">
-        <v>0.7984039343321716</v>
+        <v>0.7897053530577274</v>
       </c>
       <c r="D13">
-        <v>0.3277439343321716</v>
+        <v>0.3279853530577274</v>
       </c>
       <c r="E13">
-        <v>0.06834</v>
+        <v>0.07728</v>
       </c>
       <c r="F13">
-        <v>0.09834</v>
+        <v>0.10728</v>
       </c>
       <c r="G13">
         <v>0.569</v>
@@ -2335,28 +2335,28 @@
         <v>0.397</v>
       </c>
       <c r="M13">
-        <v>0.004946501999999999</v>
+        <v>0.005396184</v>
       </c>
       <c r="N13">
-        <v>0.3920534979999999</v>
+        <v>0.3916038159999999</v>
       </c>
       <c r="O13">
-        <v>0.1176160494</v>
+        <v>0.1174811448</v>
       </c>
       <c r="P13">
-        <v>0.2744374486</v>
+        <v>0.2741226711999999</v>
       </c>
       <c r="Q13">
-        <v>0.4524374486</v>
+        <v>0.4521226711999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1892596306416776</v>
+        <v>0.1904397300758363</v>
       </c>
       <c r="T13">
-        <v>1.000264033588541</v>
+        <v>1.008492209102219</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>80.25873637572572</v>
+        <v>73.57050834441523</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.171812162466736</v>
+        <v>0.1713101536623789</v>
       </c>
       <c r="C14">
-        <v>0.7897053530577274</v>
+        <v>0.7810071277072731</v>
       </c>
       <c r="D14">
-        <v>0.3279853530577274</v>
+        <v>0.3282271277072731</v>
       </c>
       <c r="E14">
-        <v>0.07728</v>
+        <v>0.08622</v>
       </c>
       <c r="F14">
-        <v>0.10728</v>
+        <v>0.11622</v>
       </c>
       <c r="G14">
         <v>0.569</v>
@@ -2417,28 +2417,28 @@
         <v>0.397</v>
       </c>
       <c r="M14">
-        <v>0.005396184</v>
+        <v>0.005845866</v>
       </c>
       <c r="N14">
-        <v>0.3916038159999999</v>
+        <v>0.391154134</v>
       </c>
       <c r="O14">
-        <v>0.1174811448</v>
+        <v>0.1173462402</v>
       </c>
       <c r="P14">
-        <v>0.2741226711999999</v>
+        <v>0.2738078938</v>
       </c>
       <c r="Q14">
-        <v>0.4521226711999999</v>
+        <v>0.4518078938</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1904397300758363</v>
+        <v>0.1916469582326194</v>
       </c>
       <c r="T14">
-        <v>1.008492209102219</v>
+        <v>1.016909538075982</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>73.57050834441523</v>
+        <v>67.91123847176792</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1713101536623789</v>
+        <v>0.1708081448580218</v>
       </c>
       <c r="C15">
-        <v>0.7810071277072731</v>
+        <v>0.7723092590684985</v>
       </c>
       <c r="D15">
-        <v>0.3282271277072731</v>
+        <v>0.3284692590684986</v>
       </c>
       <c r="E15">
-        <v>0.08622</v>
+        <v>0.09516000000000002</v>
       </c>
       <c r="F15">
-        <v>0.11622</v>
+        <v>0.12516</v>
       </c>
       <c r="G15">
         <v>0.569</v>
@@ -2499,28 +2499,28 @@
         <v>0.397</v>
       </c>
       <c r="M15">
-        <v>0.005845866</v>
+        <v>0.006295548000000001</v>
       </c>
       <c r="N15">
-        <v>0.391154134</v>
+        <v>0.390704452</v>
       </c>
       <c r="O15">
-        <v>0.1173462402</v>
+        <v>0.1172113356</v>
       </c>
       <c r="P15">
-        <v>0.2738078938</v>
+        <v>0.2734931164</v>
       </c>
       <c r="Q15">
-        <v>0.4518078938</v>
+        <v>0.4514931163999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1916469582326194</v>
+        <v>0.1928822614628161</v>
       </c>
       <c r="T15">
-        <v>1.016909538075982</v>
+        <v>1.025522618886345</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>67.91123847176792</v>
+        <v>63.06043572378448</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1708081448580218</v>
+        <v>0.1703061360536648</v>
       </c>
       <c r="C16">
-        <v>0.7723092590684985</v>
+        <v>0.7636117479314189</v>
       </c>
       <c r="D16">
-        <v>0.3284692590684986</v>
+        <v>0.328711747931419</v>
       </c>
       <c r="E16">
-        <v>0.09516000000000002</v>
+        <v>0.1041</v>
       </c>
       <c r="F16">
-        <v>0.12516</v>
+        <v>0.1341</v>
       </c>
       <c r="G16">
         <v>0.569</v>
@@ -2581,28 +2581,28 @@
         <v>0.397</v>
       </c>
       <c r="M16">
-        <v>0.006295548000000001</v>
+        <v>0.00674523</v>
       </c>
       <c r="N16">
-        <v>0.390704452</v>
+        <v>0.39025477</v>
       </c>
       <c r="O16">
-        <v>0.1172113356</v>
+        <v>0.117076431</v>
       </c>
       <c r="P16">
-        <v>0.2734931164</v>
+        <v>0.273178339</v>
       </c>
       <c r="Q16">
-        <v>0.4514931163999999</v>
+        <v>0.451178339</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1928822614628161</v>
+        <v>0.1941466306513703</v>
       </c>
       <c r="T16">
-        <v>1.025522618886345</v>
+        <v>1.034338360421656</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>63.06043572378448</v>
+        <v>58.85640667553218</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1703061360536648</v>
+        <v>0.1698041272493077</v>
       </c>
       <c r="C17">
-        <v>0.7636117479314189</v>
+        <v>0.7549145950883849</v>
       </c>
       <c r="D17">
-        <v>0.328711747931419</v>
+        <v>0.3289545950883849</v>
       </c>
       <c r="E17">
-        <v>0.1041</v>
+        <v>0.11304</v>
       </c>
       <c r="F17">
-        <v>0.1341</v>
+        <v>0.14304</v>
       </c>
       <c r="G17">
         <v>0.569</v>
@@ -2663,28 +2663,28 @@
         <v>0.397</v>
       </c>
       <c r="M17">
-        <v>0.00674523</v>
+        <v>0.007194911999999999</v>
       </c>
       <c r="N17">
-        <v>0.39025477</v>
+        <v>0.389805088</v>
       </c>
       <c r="O17">
-        <v>0.117076431</v>
+        <v>0.1169415264</v>
       </c>
       <c r="P17">
-        <v>0.273178339</v>
+        <v>0.2728635616</v>
       </c>
       <c r="Q17">
-        <v>0.451178339</v>
+        <v>0.4508635616</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1941466306513703</v>
+        <v>0.1954411038682234</v>
       </c>
       <c r="T17">
-        <v>1.034338360421656</v>
+        <v>1.043364000564952</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>58.85640667553219</v>
+        <v>55.17788125831143</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1698041272493077</v>
+        <v>0.1693021184449507</v>
       </c>
       <c r="C18">
-        <v>0.7549145950883849</v>
+        <v>0.7462178013340894</v>
       </c>
       <c r="D18">
-        <v>0.3289545950883849</v>
+        <v>0.3291978013340894</v>
       </c>
       <c r="E18">
-        <v>0.11304</v>
+        <v>0.12198</v>
       </c>
       <c r="F18">
-        <v>0.14304</v>
+        <v>0.15198</v>
       </c>
       <c r="G18">
         <v>0.569</v>
@@ -2745,28 +2745,28 @@
         <v>0.397</v>
       </c>
       <c r="M18">
-        <v>0.007194911999999999</v>
+        <v>0.007644594</v>
       </c>
       <c r="N18">
-        <v>0.389805088</v>
+        <v>0.389355406</v>
       </c>
       <c r="O18">
-        <v>0.1169415264</v>
+        <v>0.1168066218</v>
       </c>
       <c r="P18">
-        <v>0.2728635616</v>
+        <v>0.2725487841999999</v>
       </c>
       <c r="Q18">
-        <v>0.4508635616</v>
+        <v>0.4505487841999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1954411038682234</v>
+        <v>0.1967667692107839</v>
       </c>
       <c r="T18">
-        <v>1.043364000564952</v>
+        <v>1.052607126012905</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>55.17788125831143</v>
+        <v>51.93212353723428</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1693021184449507</v>
+        <v>0.1688001096405936</v>
       </c>
       <c r="C19">
-        <v>0.7462178013340894</v>
+        <v>0.7375213674655779</v>
       </c>
       <c r="D19">
-        <v>0.3291978013340894</v>
+        <v>0.3294413674655781</v>
       </c>
       <c r="E19">
-        <v>0.12198</v>
+        <v>0.13092</v>
       </c>
       <c r="F19">
-        <v>0.15198</v>
+        <v>0.16092</v>
       </c>
       <c r="G19">
         <v>0.569</v>
@@ -2827,28 +2827,28 @@
         <v>0.397</v>
       </c>
       <c r="M19">
-        <v>0.007644594</v>
+        <v>0.008094276000000001</v>
       </c>
       <c r="N19">
-        <v>0.389355406</v>
+        <v>0.388905724</v>
       </c>
       <c r="O19">
-        <v>0.1168066218</v>
+        <v>0.1166717172</v>
       </c>
       <c r="P19">
-        <v>0.2725487841999999</v>
+        <v>0.2722340068</v>
       </c>
       <c r="Q19">
-        <v>0.4505487841999999</v>
+        <v>0.4502340068</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1967667692107839</v>
+        <v>0.1981247678543824</v>
       </c>
       <c r="T19">
-        <v>1.052607126012905</v>
+        <v>1.062075693544954</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>51.93212353723428</v>
+        <v>49.04700556294348</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1688001096405936</v>
+        <v>0.1682981008362365</v>
       </c>
       <c r="C20">
-        <v>0.7375213674655781</v>
+        <v>0.7288252942822566</v>
       </c>
       <c r="D20">
-        <v>0.329441367465578</v>
+        <v>0.3296852942822567</v>
       </c>
       <c r="E20">
-        <v>0.13092</v>
+        <v>0.13986</v>
       </c>
       <c r="F20">
-        <v>0.16092</v>
+        <v>0.16986</v>
       </c>
       <c r="G20">
         <v>0.569</v>
@@ -2909,28 +2909,28 @@
         <v>0.397</v>
       </c>
       <c r="M20">
-        <v>0.008094275999999999</v>
+        <v>0.008543958000000001</v>
       </c>
       <c r="N20">
-        <v>0.388905724</v>
+        <v>0.3884560419999999</v>
       </c>
       <c r="O20">
-        <v>0.1166717172</v>
+        <v>0.1165368126</v>
       </c>
       <c r="P20">
-        <v>0.2722340068</v>
+        <v>0.2719192294</v>
       </c>
       <c r="Q20">
-        <v>0.4502340068</v>
+        <v>0.4499192294</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1981247678543824</v>
+        <v>0.199516297328687</v>
       </c>
       <c r="T20">
-        <v>1.062075693544954</v>
+        <v>1.071778052867919</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>49.04700556294349</v>
+        <v>46.4655842175254</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1682981008362365</v>
+        <v>0.1677960920318795</v>
       </c>
       <c r="C21">
-        <v>0.7288252942822566</v>
+        <v>0.7201295825859004</v>
       </c>
       <c r="D21">
-        <v>0.3296852942822567</v>
+        <v>0.3299295825859005</v>
       </c>
       <c r="E21">
-        <v>0.13986</v>
+        <v>0.1488</v>
       </c>
       <c r="F21">
-        <v>0.16986</v>
+        <v>0.1788</v>
       </c>
       <c r="G21">
         <v>0.569</v>
@@ -2991,28 +2991,28 @@
         <v>0.397</v>
       </c>
       <c r="M21">
-        <v>0.008543958000000001</v>
+        <v>0.008993640000000001</v>
       </c>
       <c r="N21">
-        <v>0.3884560419999999</v>
+        <v>0.3880063599999999</v>
       </c>
       <c r="O21">
-        <v>0.1165368126</v>
+        <v>0.116401908</v>
       </c>
       <c r="P21">
-        <v>0.2719192294</v>
+        <v>0.2716044519999999</v>
       </c>
       <c r="Q21">
-        <v>0.4499192294</v>
+        <v>0.4496044519999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.199516297328687</v>
+        <v>0.2009426150398493</v>
       </c>
       <c r="T21">
-        <v>1.071778052867919</v>
+        <v>1.081722971173958</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>46.4655842175254</v>
+        <v>44.14230500664913</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1677960920318795</v>
+        <v>0.1672940832275224</v>
       </c>
       <c r="C22">
-        <v>0.7201295825859004</v>
+        <v>0.7114342331806629</v>
       </c>
       <c r="D22">
-        <v>0.3299295825859005</v>
+        <v>0.330174233180663</v>
       </c>
       <c r="E22">
-        <v>0.1488</v>
+        <v>0.15774</v>
       </c>
       <c r="F22">
-        <v>0.1788</v>
+        <v>0.18774</v>
       </c>
       <c r="G22">
         <v>0.569</v>
@@ -3073,28 +3073,28 @@
         <v>0.397</v>
       </c>
       <c r="M22">
-        <v>0.008993640000000001</v>
+        <v>0.009443322000000001</v>
       </c>
       <c r="N22">
-        <v>0.3880063599999999</v>
+        <v>0.387556678</v>
       </c>
       <c r="O22">
-        <v>0.116401908</v>
+        <v>0.1162670034</v>
       </c>
       <c r="P22">
-        <v>0.2716044519999999</v>
+        <v>0.2712896746</v>
       </c>
       <c r="Q22">
-        <v>0.4496044519999999</v>
+        <v>0.4492896746</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2009426150398493</v>
+        <v>0.2024050420601549</v>
       </c>
       <c r="T22">
-        <v>1.081722971173958</v>
+        <v>1.091919659563693</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>44.14230500664913</v>
+        <v>42.04029048252299</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1672940832275224</v>
+        <v>0.1667920744231653</v>
       </c>
       <c r="C23">
-        <v>0.7114342331806629</v>
+        <v>0.7027392468730845</v>
       </c>
       <c r="D23">
-        <v>0.330174233180663</v>
+        <v>0.3304192468730845</v>
       </c>
       <c r="E23">
-        <v>0.15774</v>
+        <v>0.16668</v>
       </c>
       <c r="F23">
-        <v>0.18774</v>
+        <v>0.19668</v>
       </c>
       <c r="G23">
         <v>0.569</v>
@@ -3155,28 +3155,28 @@
         <v>0.397</v>
       </c>
       <c r="M23">
-        <v>0.009443321999999999</v>
+        <v>0.009893003999999999</v>
       </c>
       <c r="N23">
-        <v>0.387556678</v>
+        <v>0.387106996</v>
       </c>
       <c r="O23">
-        <v>0.1162670034</v>
+        <v>0.1161320988</v>
       </c>
       <c r="P23">
-        <v>0.2712896746</v>
+        <v>0.2709748972</v>
       </c>
       <c r="Q23">
-        <v>0.4492896746</v>
+        <v>0.4489748972</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2024050420601549</v>
+        <v>0.2039049672091863</v>
       </c>
       <c r="T23">
-        <v>1.091919659563693</v>
+        <v>1.102377801501883</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>42.040290482523</v>
+        <v>40.12936818786286</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1667920744231653</v>
+        <v>0.1662900656188083</v>
       </c>
       <c r="C24">
-        <v>0.7027392468730845</v>
+        <v>0.6940446244721014</v>
       </c>
       <c r="D24">
-        <v>0.3304192468730845</v>
+        <v>0.3306646244721015</v>
       </c>
       <c r="E24">
-        <v>0.16668</v>
+        <v>0.17562</v>
       </c>
       <c r="F24">
-        <v>0.19668</v>
+        <v>0.20562</v>
       </c>
       <c r="G24">
         <v>0.569</v>
@@ -3237,28 +3237,28 @@
         <v>0.397</v>
       </c>
       <c r="M24">
-        <v>0.009893003999999999</v>
+        <v>0.010342686</v>
       </c>
       <c r="N24">
-        <v>0.387106996</v>
+        <v>0.386657314</v>
       </c>
       <c r="O24">
-        <v>0.1161320988</v>
+        <v>0.1159971942</v>
       </c>
       <c r="P24">
-        <v>0.2709748972</v>
+        <v>0.2706601198</v>
       </c>
       <c r="Q24">
-        <v>0.4489748972</v>
+        <v>0.4486601198</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2039049672091863</v>
+        <v>0.2054438514529977</v>
       </c>
       <c r="T24">
-        <v>1.102377801501883</v>
+        <v>1.113107583490416</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>40.12936818786286</v>
+        <v>38.38461304926012</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1662900656188083</v>
+        <v>0.1657880568144512</v>
       </c>
       <c r="C25">
-        <v>0.6940446244721014</v>
+        <v>0.6853503667890544</v>
       </c>
       <c r="D25">
-        <v>0.3306646244721015</v>
+        <v>0.3309103667890546</v>
       </c>
       <c r="E25">
-        <v>0.17562</v>
+        <v>0.18456</v>
       </c>
       <c r="F25">
-        <v>0.20562</v>
+        <v>0.21456</v>
       </c>
       <c r="G25">
         <v>0.569</v>
@@ -3319,28 +3319,28 @@
         <v>0.397</v>
       </c>
       <c r="M25">
-        <v>0.010342686</v>
+        <v>0.010792368</v>
       </c>
       <c r="N25">
-        <v>0.386657314</v>
+        <v>0.386207632</v>
       </c>
       <c r="O25">
-        <v>0.1159971942</v>
+        <v>0.1158622896</v>
       </c>
       <c r="P25">
-        <v>0.2706601198</v>
+        <v>0.2703453424</v>
       </c>
       <c r="Q25">
-        <v>0.4486601198</v>
+        <v>0.4483453424</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2054438514529977</v>
+        <v>0.2070232326505937</v>
       </c>
       <c r="T25">
-        <v>1.113107583490416</v>
+        <v>1.124119728162858</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>38.38461304926012</v>
+        <v>36.78525417220762</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1657880568144512</v>
+        <v>0.1652860480100941</v>
       </c>
       <c r="C26">
-        <v>0.6853503667890545</v>
+        <v>0.6766564746376984</v>
       </c>
       <c r="D26">
-        <v>0.3309103667890546</v>
+        <v>0.3311564746376985</v>
       </c>
       <c r="E26">
-        <v>0.18456</v>
+        <v>0.1935</v>
       </c>
       <c r="F26">
-        <v>0.21456</v>
+        <v>0.2235</v>
       </c>
       <c r="G26">
         <v>0.569</v>
@@ -3401,28 +3401,28 @@
         <v>0.397</v>
       </c>
       <c r="M26">
-        <v>0.010792368</v>
+        <v>0.01124205</v>
       </c>
       <c r="N26">
-        <v>0.386207632</v>
+        <v>0.38575795</v>
       </c>
       <c r="O26">
-        <v>0.1158622896</v>
+        <v>0.115727385</v>
       </c>
       <c r="P26">
-        <v>0.2703453424</v>
+        <v>0.270030565</v>
       </c>
       <c r="Q26">
-        <v>0.4483453424</v>
+        <v>0.448030565</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2070232326505937</v>
+        <v>0.2086447306801255</v>
       </c>
       <c r="T26">
-        <v>1.124119728162858</v>
+        <v>1.135425530026565</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>36.78525417220762</v>
+        <v>35.31384400531931</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1652860480100941</v>
+        <v>0.1647840392057371</v>
       </c>
       <c r="C27">
-        <v>0.6766564746376984</v>
+        <v>0.6679629488342105</v>
       </c>
       <c r="D27">
-        <v>0.3311564746376985</v>
+        <v>0.3314029488342106</v>
       </c>
       <c r="E27">
-        <v>0.1935</v>
+        <v>0.20244</v>
       </c>
       <c r="F27">
-        <v>0.2235</v>
+        <v>0.23244</v>
       </c>
       <c r="G27">
         <v>0.569</v>
@@ -3483,28 +3483,28 @@
         <v>0.397</v>
       </c>
       <c r="M27">
-        <v>0.01124205</v>
+        <v>0.011691732</v>
       </c>
       <c r="N27">
-        <v>0.38575795</v>
+        <v>0.385308268</v>
       </c>
       <c r="O27">
-        <v>0.115727385</v>
+        <v>0.1155924804</v>
       </c>
       <c r="P27">
-        <v>0.270030565</v>
+        <v>0.2697157876</v>
       </c>
       <c r="Q27">
-        <v>0.448030565</v>
+        <v>0.4477157876</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2086447306801255</v>
+        <v>0.2103100529807258</v>
       </c>
       <c r="T27">
-        <v>1.135425530026565</v>
+        <v>1.147036894102805</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>35.31384400531931</v>
+        <v>33.95561923588395</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1647840392057371</v>
+        <v>0.16428203040138</v>
       </c>
       <c r="C28">
-        <v>0.6679629488342105</v>
+        <v>0.6592697901971997</v>
       </c>
       <c r="D28">
-        <v>0.3314029488342106</v>
+        <v>0.3316497901971998</v>
       </c>
       <c r="E28">
-        <v>0.20244</v>
+        <v>0.21138</v>
       </c>
       <c r="F28">
-        <v>0.23244</v>
+        <v>0.24138</v>
       </c>
       <c r="G28">
         <v>0.569</v>
@@ -3565,28 +3565,28 @@
         <v>0.397</v>
       </c>
       <c r="M28">
-        <v>0.011691732</v>
+        <v>0.012141414</v>
       </c>
       <c r="N28">
-        <v>0.385308268</v>
+        <v>0.3848585859999999</v>
       </c>
       <c r="O28">
-        <v>0.1155924804</v>
+        <v>0.1154575758</v>
       </c>
       <c r="P28">
-        <v>0.2697157876</v>
+        <v>0.2694010102</v>
       </c>
       <c r="Q28">
-        <v>0.4477157876</v>
+        <v>0.4474010101999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2103100529807258</v>
+        <v>0.2120210005498357</v>
       </c>
       <c r="T28">
-        <v>1.147036894102805</v>
+        <v>1.158966377742777</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>33.95561923588395</v>
+        <v>32.69800370862899</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.16428203040138</v>
+        <v>0.163780021597023</v>
       </c>
       <c r="C29">
-        <v>0.6592697901971997</v>
+        <v>0.6505769995477155</v>
       </c>
       <c r="D29">
-        <v>0.3316497901971998</v>
+        <v>0.3318969995477157</v>
       </c>
       <c r="E29">
-        <v>0.21138</v>
+        <v>0.22032</v>
       </c>
       <c r="F29">
-        <v>0.24138</v>
+        <v>0.25032</v>
       </c>
       <c r="G29">
         <v>0.569</v>
@@ -3647,28 +3647,28 @@
         <v>0.397</v>
       </c>
       <c r="M29">
-        <v>0.012141414</v>
+        <v>0.012591096</v>
       </c>
       <c r="N29">
-        <v>0.3848585859999999</v>
+        <v>0.3844089039999999</v>
       </c>
       <c r="O29">
-        <v>0.1154575758</v>
+        <v>0.1153226712</v>
       </c>
       <c r="P29">
-        <v>0.2694010102</v>
+        <v>0.2690862328</v>
       </c>
       <c r="Q29">
-        <v>0.4474010101999999</v>
+        <v>0.4470862328</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2120210005498357</v>
+        <v>0.2137794744403097</v>
       </c>
       <c r="T29">
-        <v>1.158966377742777</v>
+        <v>1.171227235928304</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>32.69800370862899</v>
+        <v>31.53021786189224</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.163780021597023</v>
+        <v>0.1632780127926659</v>
       </c>
       <c r="C30">
-        <v>0.6505769995477155</v>
+        <v>0.6418845777092579</v>
       </c>
       <c r="D30">
-        <v>0.3318969995477157</v>
+        <v>0.3321445777092579</v>
       </c>
       <c r="E30">
-        <v>0.22032</v>
+        <v>0.22926</v>
       </c>
       <c r="F30">
-        <v>0.25032</v>
+        <v>0.25926</v>
       </c>
       <c r="G30">
         <v>0.569</v>
@@ -3729,28 +3729,28 @@
         <v>0.397</v>
       </c>
       <c r="M30">
-        <v>0.012591096</v>
+        <v>0.013040778</v>
       </c>
       <c r="N30">
-        <v>0.3844089039999999</v>
+        <v>0.383959222</v>
       </c>
       <c r="O30">
-        <v>0.1153226712</v>
+        <v>0.1151877666</v>
       </c>
       <c r="P30">
-        <v>0.2690862328</v>
+        <v>0.2687714554</v>
       </c>
       <c r="Q30">
-        <v>0.4470862328</v>
+        <v>0.4467714554</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2137794744403097</v>
+        <v>0.2155874828065717</v>
       </c>
       <c r="T30">
-        <v>1.171227235928304</v>
+        <v>1.183833470400747</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>31.53021786189224</v>
+        <v>30.44296897010285</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1632780127926659</v>
+        <v>0.1627760039883088</v>
       </c>
       <c r="C31">
-        <v>0.6418845777092579</v>
+        <v>0.633192525507785</v>
       </c>
       <c r="D31">
-        <v>0.3321445777092579</v>
+        <v>0.332392525507785</v>
       </c>
       <c r="E31">
-        <v>0.22926</v>
+        <v>0.2382</v>
       </c>
       <c r="F31">
-        <v>0.25926</v>
+        <v>0.2682</v>
       </c>
       <c r="G31">
         <v>0.569</v>
@@ -3811,28 +3811,28 @@
         <v>0.397</v>
       </c>
       <c r="M31">
-        <v>0.013040778</v>
+        <v>0.01349046</v>
       </c>
       <c r="N31">
-        <v>0.383959222</v>
+        <v>0.38350954</v>
       </c>
       <c r="O31">
-        <v>0.1151877666</v>
+        <v>0.115052862</v>
       </c>
       <c r="P31">
-        <v>0.2687714554</v>
+        <v>0.268456678</v>
       </c>
       <c r="Q31">
-        <v>0.4467714554</v>
+        <v>0.446456678</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2155874828065717</v>
+        <v>0.2174471485547269</v>
       </c>
       <c r="T31">
-        <v>1.183833470400747</v>
+        <v>1.196799883000974</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>30.44296897010286</v>
+        <v>29.4282033377661</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1627760039883088</v>
+        <v>0.1622739951839518</v>
       </c>
       <c r="C32">
-        <v>0.633192525507785</v>
+        <v>0.6245008437717237</v>
       </c>
       <c r="D32">
-        <v>0.332392525507785</v>
+        <v>0.3326408437717236</v>
       </c>
       <c r="E32">
-        <v>0.2382</v>
+        <v>0.24714</v>
       </c>
       <c r="F32">
-        <v>0.2682</v>
+        <v>0.27714</v>
       </c>
       <c r="G32">
         <v>0.569</v>
@@ -3893,28 +3893,28 @@
         <v>0.397</v>
       </c>
       <c r="M32">
-        <v>0.01349046</v>
+        <v>0.013940142</v>
       </c>
       <c r="N32">
-        <v>0.38350954</v>
+        <v>0.383059858</v>
       </c>
       <c r="O32">
-        <v>0.115052862</v>
+        <v>0.1149179574</v>
       </c>
       <c r="P32">
-        <v>0.268456678</v>
+        <v>0.2681419006</v>
       </c>
       <c r="Q32">
-        <v>0.446456678</v>
+        <v>0.4461419006</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2174471485547269</v>
+        <v>0.2193607176579011</v>
       </c>
       <c r="T32">
-        <v>1.196799883000974</v>
+        <v>1.210142133647585</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>29.4282033377661</v>
+        <v>28.47890645590267</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1622739951839518</v>
+        <v>0.1617719863795947</v>
       </c>
       <c r="C33">
-        <v>0.6245008437717237</v>
+        <v>0.6158095333319779</v>
       </c>
       <c r="D33">
-        <v>0.3326408437717236</v>
+        <v>0.3328895333319779</v>
       </c>
       <c r="E33">
-        <v>0.24714</v>
+        <v>0.25608</v>
       </c>
       <c r="F33">
-        <v>0.27714</v>
+        <v>0.28608</v>
       </c>
       <c r="G33">
         <v>0.569</v>
@@ -3975,28 +3975,28 @@
         <v>0.397</v>
       </c>
       <c r="M33">
-        <v>0.013940142</v>
+        <v>0.014389824</v>
       </c>
       <c r="N33">
-        <v>0.383059858</v>
+        <v>0.382610176</v>
       </c>
       <c r="O33">
-        <v>0.1149179574</v>
+        <v>0.1147830528</v>
       </c>
       <c r="P33">
-        <v>0.2681419006</v>
+        <v>0.2678271232</v>
       </c>
       <c r="Q33">
-        <v>0.4461419006</v>
+        <v>0.4458271232</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2193607176579011</v>
+        <v>0.2213305682052863</v>
       </c>
       <c r="T33">
-        <v>1.210142133647585</v>
+        <v>1.22387680343086</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>28.47890645590267</v>
+        <v>27.58894062915572</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1617719863795947</v>
+        <v>0.1612699775752376</v>
       </c>
       <c r="C34">
-        <v>0.6158095333319779</v>
+        <v>0.6071185950219384</v>
       </c>
       <c r="D34">
-        <v>0.3328895333319779</v>
+        <v>0.3331385950219386</v>
       </c>
       <c r="E34">
-        <v>0.25608</v>
+        <v>0.26502</v>
       </c>
       <c r="F34">
-        <v>0.28608</v>
+        <v>0.29502</v>
       </c>
       <c r="G34">
         <v>0.569</v>
@@ -4057,28 +4057,28 @@
         <v>0.397</v>
       </c>
       <c r="M34">
-        <v>0.014389824</v>
+        <v>0.014839506</v>
       </c>
       <c r="N34">
-        <v>0.382610176</v>
+        <v>0.382160494</v>
       </c>
       <c r="O34">
-        <v>0.1147830528</v>
+        <v>0.1146481482</v>
       </c>
       <c r="P34">
-        <v>0.2678271232</v>
+        <v>0.2675123458</v>
       </c>
       <c r="Q34">
-        <v>0.4458271232</v>
+        <v>0.4455123458</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2213305682052863</v>
+        <v>0.2233592202615488</v>
       </c>
       <c r="T34">
-        <v>1.22387680343086</v>
+        <v>1.238021463356921</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>27.58894062915572</v>
+        <v>26.75291212524191</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1612699775752376</v>
+        <v>0.1607679687708805</v>
       </c>
       <c r="C35">
-        <v>0.6071185950219384</v>
+        <v>0.5984280296774924</v>
       </c>
       <c r="D35">
-        <v>0.3331385950219386</v>
+        <v>0.3333880296774924</v>
       </c>
       <c r="E35">
-        <v>0.26502</v>
+        <v>0.27396</v>
       </c>
       <c r="F35">
-        <v>0.29502</v>
+        <v>0.30396</v>
       </c>
       <c r="G35">
         <v>0.569</v>
@@ -4139,28 +4139,28 @@
         <v>0.397</v>
       </c>
       <c r="M35">
-        <v>0.014839506</v>
+        <v>0.015289188</v>
       </c>
       <c r="N35">
-        <v>0.382160494</v>
+        <v>0.381710812</v>
       </c>
       <c r="O35">
-        <v>0.1146481482</v>
+        <v>0.1145132436</v>
       </c>
       <c r="P35">
-        <v>0.2675123458</v>
+        <v>0.2671975684</v>
       </c>
       <c r="Q35">
-        <v>0.4455123458</v>
+        <v>0.4451975684</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2233592202615488</v>
+        <v>0.2254493466225463</v>
       </c>
       <c r="T35">
-        <v>1.238021463356921</v>
+        <v>1.252594749341346</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>26.75291212524191</v>
+        <v>25.96606176861714</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1607679687708805</v>
+        <v>0.1602659599665235</v>
       </c>
       <c r="C36">
-        <v>0.5984280296774924</v>
+        <v>0.5897378381370315</v>
       </c>
       <c r="D36">
-        <v>0.3333880296774924</v>
+        <v>0.3336378381370315</v>
       </c>
       <c r="E36">
-        <v>0.27396</v>
+        <v>0.2829</v>
       </c>
       <c r="F36">
-        <v>0.30396</v>
+        <v>0.3129</v>
       </c>
       <c r="G36">
         <v>0.569</v>
@@ -4221,28 +4221,28 @@
         <v>0.397</v>
       </c>
       <c r="M36">
-        <v>0.015289188</v>
+        <v>0.01573887</v>
       </c>
       <c r="N36">
-        <v>0.381710812</v>
+        <v>0.3812611299999999</v>
       </c>
       <c r="O36">
-        <v>0.1145132436</v>
+        <v>0.114378339</v>
       </c>
       <c r="P36">
-        <v>0.2671975684</v>
+        <v>0.266882791</v>
       </c>
       <c r="Q36">
-        <v>0.4451975684</v>
+        <v>0.4448827909999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2254493466225463</v>
+        <v>0.2276037845638823</v>
       </c>
       <c r="T36">
-        <v>1.252594749341346</v>
+        <v>1.267616444125292</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>25.96606176861714</v>
+        <v>25.22417428951379</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1602659599665235</v>
+        <v>0.1597639511621665</v>
       </c>
       <c r="C37">
-        <v>0.5897378381370315</v>
+        <v>0.5810480212414624</v>
       </c>
       <c r="D37">
-        <v>0.3336378381370315</v>
+        <v>0.3338880212414626</v>
       </c>
       <c r="E37">
-        <v>0.2829</v>
+        <v>0.29184</v>
       </c>
       <c r="F37">
-        <v>0.3129</v>
+        <v>0.3218400000000001</v>
       </c>
       <c r="G37">
         <v>0.569</v>
@@ -4303,28 +4303,28 @@
         <v>0.397</v>
       </c>
       <c r="M37">
-        <v>0.01573887</v>
+        <v>0.016188552</v>
       </c>
       <c r="N37">
-        <v>0.3812611299999999</v>
+        <v>0.3808114479999999</v>
       </c>
       <c r="O37">
-        <v>0.114378339</v>
+        <v>0.1142434344</v>
       </c>
       <c r="P37">
-        <v>0.266882791</v>
+        <v>0.2665680135999999</v>
       </c>
       <c r="Q37">
-        <v>0.4448827909999999</v>
+        <v>0.4445680135999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2276037845638823</v>
+        <v>0.2298255486908851</v>
       </c>
       <c r="T37">
-        <v>1.267616444125292</v>
+        <v>1.283107566871237</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>25.22417428951379</v>
+        <v>24.52350278147174</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1597639511621665</v>
+        <v>0.1592619423578094</v>
       </c>
       <c r="C38">
-        <v>0.5810480212414624</v>
+        <v>0.5723585798342166</v>
       </c>
       <c r="D38">
-        <v>0.3338880212414624</v>
+        <v>0.3341385798342166</v>
       </c>
       <c r="E38">
-        <v>0.29184</v>
+        <v>0.30078</v>
       </c>
       <c r="F38">
-        <v>0.32184</v>
+        <v>0.33078</v>
       </c>
       <c r="G38">
         <v>0.569</v>
@@ -4385,28 +4385,28 @@
         <v>0.397</v>
       </c>
       <c r="M38">
-        <v>0.016188552</v>
+        <v>0.016638234</v>
       </c>
       <c r="N38">
-        <v>0.3808114479999999</v>
+        <v>0.3803617659999999</v>
       </c>
       <c r="O38">
-        <v>0.1142434344</v>
+        <v>0.1141085298</v>
       </c>
       <c r="P38">
-        <v>0.2665680135999999</v>
+        <v>0.2662532362</v>
       </c>
       <c r="Q38">
-        <v>0.4445680135999999</v>
+        <v>0.4442532362</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2298255486908851</v>
+        <v>0.2321178450123959</v>
       </c>
       <c r="T38">
-        <v>1.283107566871237</v>
+        <v>1.299090471291656</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>24.52350278147174</v>
+        <v>23.86070540899953</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1592619423578094</v>
+        <v>0.1587599335534523</v>
       </c>
       <c r="C39">
-        <v>0.5723585798342166</v>
+        <v>0.563669514761258</v>
       </c>
       <c r="D39">
-        <v>0.3341385798342166</v>
+        <v>0.3343895147612582</v>
       </c>
       <c r="E39">
-        <v>0.30078</v>
+        <v>0.30972</v>
       </c>
       <c r="F39">
-        <v>0.33078</v>
+        <v>0.33972</v>
       </c>
       <c r="G39">
         <v>0.569</v>
@@ -4467,28 +4467,28 @@
         <v>0.397</v>
       </c>
       <c r="M39">
-        <v>0.016638234</v>
+        <v>0.017087916</v>
       </c>
       <c r="N39">
-        <v>0.3803617659999999</v>
+        <v>0.379912084</v>
       </c>
       <c r="O39">
-        <v>0.1141085298</v>
+        <v>0.1139736252</v>
       </c>
       <c r="P39">
-        <v>0.2662532362</v>
+        <v>0.2659384588</v>
       </c>
       <c r="Q39">
-        <v>0.4442532362</v>
+        <v>0.4439384588</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2321178450123959</v>
+        <v>0.234484086376536</v>
       </c>
       <c r="T39">
-        <v>1.299090471291656</v>
+        <v>1.315588953274024</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>23.86070540899953</v>
+        <v>23.23279210876271</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1587599335534523</v>
+        <v>0.1582579247490953</v>
       </c>
       <c r="C40">
-        <v>0.563669514761258</v>
+        <v>0.554980826871095</v>
       </c>
       <c r="D40">
-        <v>0.3343895147612582</v>
+        <v>0.334640826871095</v>
       </c>
       <c r="E40">
-        <v>0.30972</v>
+        <v>0.31866</v>
       </c>
       <c r="F40">
-        <v>0.33972</v>
+        <v>0.34866</v>
       </c>
       <c r="G40">
         <v>0.569</v>
@@ -4549,28 +4549,28 @@
         <v>0.397</v>
       </c>
       <c r="M40">
-        <v>0.017087916</v>
+        <v>0.017537598</v>
       </c>
       <c r="N40">
-        <v>0.379912084</v>
+        <v>0.379462402</v>
       </c>
       <c r="O40">
-        <v>0.1139736252</v>
+        <v>0.1138387206</v>
       </c>
       <c r="P40">
-        <v>0.2659384588</v>
+        <v>0.2656236814</v>
       </c>
       <c r="Q40">
-        <v>0.4439384588</v>
+        <v>0.4436236814</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.234484086376536</v>
+        <v>0.2369279094247463</v>
       </c>
       <c r="T40">
-        <v>1.315588953274024</v>
+        <v>1.332628369091879</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>23.23279210876271</v>
+        <v>22.6370794905893</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1582579247490953</v>
+        <v>0.1577559159447382</v>
       </c>
       <c r="C41">
-        <v>0.554980826871095</v>
+        <v>0.5462925170147875</v>
       </c>
       <c r="D41">
-        <v>0.334640826871095</v>
+        <v>0.3348925170147877</v>
       </c>
       <c r="E41">
-        <v>0.31866</v>
+        <v>0.3276</v>
       </c>
       <c r="F41">
-        <v>0.34866</v>
+        <v>0.3576</v>
       </c>
       <c r="G41">
         <v>0.569</v>
@@ -4631,28 +4631,28 @@
         <v>0.397</v>
       </c>
       <c r="M41">
-        <v>0.017537598</v>
+        <v>0.01798728</v>
       </c>
       <c r="N41">
-        <v>0.379462402</v>
+        <v>0.37901272</v>
       </c>
       <c r="O41">
-        <v>0.1138387206</v>
+        <v>0.113703816</v>
       </c>
       <c r="P41">
-        <v>0.2656236814</v>
+        <v>0.265308904</v>
       </c>
       <c r="Q41">
-        <v>0.4436236814</v>
+        <v>0.4433089039999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2369279094247463</v>
+        <v>0.2394531932412304</v>
       </c>
       <c r="T41">
-        <v>1.332628369091879</v>
+        <v>1.350235765436997</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>22.6370794905893</v>
+        <v>22.07115250332457</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1577559159447382</v>
+        <v>0.1572539071403811</v>
       </c>
       <c r="C42">
-        <v>0.5462925170147875</v>
+        <v>0.5376045860459586</v>
       </c>
       <c r="D42">
-        <v>0.3348925170147877</v>
+        <v>0.3351445860459588</v>
       </c>
       <c r="E42">
-        <v>0.3276</v>
+        <v>0.33654</v>
       </c>
       <c r="F42">
-        <v>0.3576</v>
+        <v>0.36654</v>
       </c>
       <c r="G42">
         <v>0.569</v>
@@ -4713,28 +4713,28 @@
         <v>0.397</v>
       </c>
       <c r="M42">
-        <v>0.01798728</v>
+        <v>0.018436962</v>
       </c>
       <c r="N42">
-        <v>0.37901272</v>
+        <v>0.378563038</v>
       </c>
       <c r="O42">
-        <v>0.113703816</v>
+        <v>0.1135689114</v>
       </c>
       <c r="P42">
-        <v>0.265308904</v>
+        <v>0.2649941266</v>
       </c>
       <c r="Q42">
-        <v>0.4433089039999999</v>
+        <v>0.4429941266</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2394531932412304</v>
+        <v>0.2420640798989511</v>
       </c>
       <c r="T42">
-        <v>1.350235765436997</v>
+        <v>1.368440022675169</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>22.07115250332457</v>
+        <v>21.53283171056055</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1572539071403811</v>
+        <v>0.1567518983360241</v>
       </c>
       <c r="C43">
-        <v>0.5376045860459586</v>
+        <v>0.5289170348208032</v>
       </c>
       <c r="D43">
-        <v>0.3351445860459588</v>
+        <v>0.3353970348208032</v>
       </c>
       <c r="E43">
-        <v>0.33654</v>
+        <v>0.34548</v>
       </c>
       <c r="F43">
-        <v>0.36654</v>
+        <v>0.37548</v>
       </c>
       <c r="G43">
         <v>0.569</v>
@@ -4795,28 +4795,28 @@
         <v>0.397</v>
       </c>
       <c r="M43">
-        <v>0.018436962</v>
+        <v>0.018886644</v>
       </c>
       <c r="N43">
-        <v>0.378563038</v>
+        <v>0.378113356</v>
       </c>
       <c r="O43">
-        <v>0.1135689114</v>
+        <v>0.1134340068</v>
       </c>
       <c r="P43">
-        <v>0.2649941266</v>
+        <v>0.2646793492</v>
       </c>
       <c r="Q43">
-        <v>0.4429941266</v>
+        <v>0.4426793492</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2420640798989511</v>
+        <v>0.244764997131076</v>
       </c>
       <c r="T43">
-        <v>1.368440022675169</v>
+        <v>1.387272012921554</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>21.53283171056055</v>
+        <v>21.02014524126149</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1567518983360241</v>
+        <v>0.156249889531667</v>
       </c>
       <c r="C44">
-        <v>0.5289170348208032</v>
+        <v>0.5202298641980974</v>
       </c>
       <c r="D44">
-        <v>0.3353970348208032</v>
+        <v>0.3356498641980974</v>
       </c>
       <c r="E44">
-        <v>0.34548</v>
+        <v>0.35442</v>
       </c>
       <c r="F44">
-        <v>0.37548</v>
+        <v>0.38442</v>
       </c>
       <c r="G44">
         <v>0.569</v>
@@ -4877,28 +4877,28 @@
         <v>0.397</v>
       </c>
       <c r="M44">
-        <v>0.018886644</v>
+        <v>0.019336326</v>
       </c>
       <c r="N44">
-        <v>0.378113356</v>
+        <v>0.3776636739999999</v>
       </c>
       <c r="O44">
-        <v>0.1134340068</v>
+        <v>0.1132991022</v>
       </c>
       <c r="P44">
-        <v>0.2646793492</v>
+        <v>0.2643645717999999</v>
       </c>
       <c r="Q44">
-        <v>0.4426793492</v>
+        <v>0.4423645717999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.244764997131076</v>
+        <v>0.2475606833888895</v>
       </c>
       <c r="T44">
-        <v>1.387272012921553</v>
+        <v>1.406764774755531</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>21.0201452412615</v>
+        <v>20.53130465425541</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.156249889531667</v>
+        <v>0.15574788072731</v>
       </c>
       <c r="C45">
-        <v>0.5202298641980974</v>
+        <v>0.5115430750392091</v>
       </c>
       <c r="D45">
-        <v>0.3356498641980974</v>
+        <v>0.3359030750392091</v>
       </c>
       <c r="E45">
-        <v>0.35442</v>
+        <v>0.36336</v>
       </c>
       <c r="F45">
-        <v>0.38442</v>
+        <v>0.39336</v>
       </c>
       <c r="G45">
         <v>0.569</v>
@@ -4959,28 +4959,28 @@
         <v>0.397</v>
       </c>
       <c r="M45">
-        <v>0.019336326</v>
+        <v>0.019786008</v>
       </c>
       <c r="N45">
-        <v>0.3776636739999999</v>
+        <v>0.3772139919999999</v>
       </c>
       <c r="O45">
-        <v>0.1132991022</v>
+        <v>0.1131641976</v>
       </c>
       <c r="P45">
-        <v>0.2643645717999999</v>
+        <v>0.2640497944</v>
       </c>
       <c r="Q45">
-        <v>0.4423645717999999</v>
+        <v>0.4420497944</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2475606833888895</v>
+        <v>0.2504562155844821</v>
       </c>
       <c r="T45">
-        <v>1.406764774755531</v>
+        <v>1.426953706655008</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>20.53130465425541</v>
+        <v>20.06468409393143</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.15574788072731</v>
+        <v>0.1552458719229529</v>
       </c>
       <c r="C46">
-        <v>0.5115430750392091</v>
+        <v>0.5028566682081074</v>
       </c>
       <c r="D46">
-        <v>0.3359030750392091</v>
+        <v>0.3361566682081075</v>
       </c>
       <c r="E46">
-        <v>0.36336</v>
+        <v>0.3723</v>
       </c>
       <c r="F46">
-        <v>0.39336</v>
+        <v>0.4023</v>
       </c>
       <c r="G46">
         <v>0.569</v>
@@ -5041,28 +5041,28 @@
         <v>0.397</v>
       </c>
       <c r="M46">
-        <v>0.019786008</v>
+        <v>0.02023569</v>
       </c>
       <c r="N46">
-        <v>0.3772139919999999</v>
+        <v>0.37676431</v>
       </c>
       <c r="O46">
-        <v>0.1131641976</v>
+        <v>0.113029293</v>
       </c>
       <c r="P46">
-        <v>0.2640497944</v>
+        <v>0.263735017</v>
       </c>
       <c r="Q46">
-        <v>0.4420497944</v>
+        <v>0.441735017</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2504562155844821</v>
+        <v>0.2534570398599144</v>
       </c>
       <c r="T46">
-        <v>1.426953706655008</v>
+        <v>1.447876781532647</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>20.06468409393143</v>
+        <v>19.6188022251774</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1552458719229529</v>
+        <v>0.1547438631185958</v>
       </c>
       <c r="C47">
-        <v>0.5028566682081074</v>
+        <v>0.4941706445713724</v>
       </c>
       <c r="D47">
-        <v>0.3361566682081075</v>
+        <v>0.3364106445713725</v>
       </c>
       <c r="E47">
-        <v>0.3723</v>
+        <v>0.38124</v>
       </c>
       <c r="F47">
-        <v>0.4023</v>
+        <v>0.41124</v>
       </c>
       <c r="G47">
         <v>0.569</v>
@@ -5123,28 +5123,28 @@
         <v>0.397</v>
       </c>
       <c r="M47">
-        <v>0.02023569</v>
+        <v>0.020685372</v>
       </c>
       <c r="N47">
-        <v>0.37676431</v>
+        <v>0.376314628</v>
       </c>
       <c r="O47">
-        <v>0.113029293</v>
+        <v>0.1128943884</v>
       </c>
       <c r="P47">
-        <v>0.263735017</v>
+        <v>0.2634202396</v>
       </c>
       <c r="Q47">
-        <v>0.441735017</v>
+        <v>0.4414202396</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2534570398599144</v>
+        <v>0.2565690057751774</v>
       </c>
       <c r="T47">
-        <v>1.447876781532647</v>
+        <v>1.469574785109458</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>19.6188022251774</v>
+        <v>19.19230652463006</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1547438631185958</v>
+        <v>0.1542418543142388</v>
       </c>
       <c r="C48">
-        <v>0.4941706445713724</v>
+        <v>0.4854850049982051</v>
       </c>
       <c r="D48">
-        <v>0.3364106445713725</v>
+        <v>0.3366650049982051</v>
       </c>
       <c r="E48">
-        <v>0.38124</v>
+        <v>0.39018</v>
       </c>
       <c r="F48">
-        <v>0.41124</v>
+        <v>0.4201800000000001</v>
       </c>
       <c r="G48">
         <v>0.569</v>
@@ -5205,28 +5205,28 @@
         <v>0.397</v>
       </c>
       <c r="M48">
-        <v>0.020685372</v>
+        <v>0.021135054</v>
       </c>
       <c r="N48">
-        <v>0.376314628</v>
+        <v>0.375864946</v>
       </c>
       <c r="O48">
-        <v>0.1128943884</v>
+        <v>0.1127594838</v>
       </c>
       <c r="P48">
-        <v>0.2634202396</v>
+        <v>0.2631054622</v>
       </c>
       <c r="Q48">
-        <v>0.4414202396</v>
+        <v>0.4411054622</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2565690057751774</v>
+        <v>0.2597984043664883</v>
       </c>
       <c r="T48">
-        <v>1.469574785109458</v>
+        <v>1.492091581274074</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>19.19230652463006</v>
+        <v>18.78395957729751</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1542418543142388</v>
+        <v>0.1537398455098817</v>
       </c>
       <c r="C49">
-        <v>0.4854850049982051</v>
+        <v>0.476799750360437</v>
       </c>
       <c r="D49">
-        <v>0.3366650049982051</v>
+        <v>0.3369197503604371</v>
       </c>
       <c r="E49">
-        <v>0.39018</v>
+        <v>0.39912</v>
       </c>
       <c r="F49">
-        <v>0.4201800000000001</v>
+        <v>0.4291200000000001</v>
       </c>
       <c r="G49">
         <v>0.569</v>
@@ -5287,28 +5287,28 @@
         <v>0.397</v>
       </c>
       <c r="M49">
-        <v>0.021135054</v>
+        <v>0.021584736</v>
       </c>
       <c r="N49">
-        <v>0.375864946</v>
+        <v>0.375415264</v>
       </c>
       <c r="O49">
-        <v>0.1127594838</v>
+        <v>0.1126245792</v>
       </c>
       <c r="P49">
-        <v>0.2631054622</v>
+        <v>0.2627906848</v>
       </c>
       <c r="Q49">
-        <v>0.4411054622</v>
+        <v>0.4407906848</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2597984043664883</v>
+        <v>0.2631520105959264</v>
       </c>
       <c r="T49">
-        <v>1.492091581274074</v>
+        <v>1.515474408060405</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>18.78395957729751</v>
+        <v>18.39262708610381</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1537398455098817</v>
+        <v>0.1532378367055246</v>
       </c>
       <c r="C50">
-        <v>0.476799750360437</v>
+        <v>0.4681148815325408</v>
       </c>
       <c r="D50">
-        <v>0.3369197503604371</v>
+        <v>0.3371748815325409</v>
       </c>
       <c r="E50">
-        <v>0.39912</v>
+        <v>0.40806</v>
       </c>
       <c r="F50">
-        <v>0.42912</v>
+        <v>0.43806</v>
       </c>
       <c r="G50">
         <v>0.569</v>
@@ -5369,28 +5369,28 @@
         <v>0.397</v>
       </c>
       <c r="M50">
-        <v>0.021584736</v>
+        <v>0.022034418</v>
       </c>
       <c r="N50">
-        <v>0.375415264</v>
+        <v>0.374965582</v>
       </c>
       <c r="O50">
-        <v>0.1126245792</v>
+        <v>0.1124896746</v>
       </c>
       <c r="P50">
-        <v>0.2627906848</v>
+        <v>0.2624759074</v>
       </c>
       <c r="Q50">
-        <v>0.4407906848</v>
+        <v>0.4404759074</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2631520105959264</v>
+        <v>0.2666371307951463</v>
       </c>
       <c r="T50">
-        <v>1.515474408060405</v>
+        <v>1.5397742084462</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>18.39262708610381</v>
+        <v>18.01726734965271</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1532378367055246</v>
+        <v>0.1527358279011676</v>
       </c>
       <c r="C51">
-        <v>0.4681148815325408</v>
+        <v>0.4594303993916397</v>
       </c>
       <c r="D51">
-        <v>0.3371748815325409</v>
+        <v>0.3374303993916398</v>
       </c>
       <c r="E51">
-        <v>0.40806</v>
+        <v>0.417</v>
       </c>
       <c r="F51">
-        <v>0.43806</v>
+        <v>0.447</v>
       </c>
       <c r="G51">
         <v>0.569</v>
@@ -5451,28 +5451,28 @@
         <v>0.397</v>
       </c>
       <c r="M51">
-        <v>0.022034418</v>
+        <v>0.0224841</v>
       </c>
       <c r="N51">
-        <v>0.374965582</v>
+        <v>0.3745159</v>
       </c>
       <c r="O51">
-        <v>0.1124896746</v>
+        <v>0.11235477</v>
       </c>
       <c r="P51">
-        <v>0.2624759074</v>
+        <v>0.26216113</v>
       </c>
       <c r="Q51">
-        <v>0.4404759074</v>
+        <v>0.44016113</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2666371307951463</v>
+        <v>0.2702616558023352</v>
       </c>
       <c r="T51">
-        <v>1.5397742084462</v>
+        <v>1.565046000847428</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>18.01726734965271</v>
+        <v>17.65692200265966</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1527358279011676</v>
+        <v>0.1522338190968105</v>
       </c>
       <c r="C52">
-        <v>0.4594303993916397</v>
+        <v>0.4507463048175179</v>
       </c>
       <c r="D52">
-        <v>0.3374303993916398</v>
+        <v>0.3376863048175179</v>
       </c>
       <c r="E52">
-        <v>0.417</v>
+        <v>0.42594</v>
       </c>
       <c r="F52">
-        <v>0.447</v>
+        <v>0.45594</v>
       </c>
       <c r="G52">
         <v>0.569</v>
@@ -5533,28 +5533,28 @@
         <v>0.397</v>
       </c>
       <c r="M52">
-        <v>0.0224841</v>
+        <v>0.022933782</v>
       </c>
       <c r="N52">
-        <v>0.3745159</v>
+        <v>0.374066218</v>
       </c>
       <c r="O52">
-        <v>0.11235477</v>
+        <v>0.1122198654</v>
       </c>
       <c r="P52">
-        <v>0.26216113</v>
+        <v>0.2618463526</v>
       </c>
       <c r="Q52">
-        <v>0.44016113</v>
+        <v>0.4398463526</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2702616558023352</v>
+        <v>0.2740341206057357</v>
       </c>
       <c r="T52">
-        <v>1.565046000847428</v>
+        <v>1.591349294979317</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>17.65692200265966</v>
+        <v>17.31070784574476</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1522338190968105</v>
+        <v>0.1517318102924534</v>
       </c>
       <c r="C53">
-        <v>0.4507463048175179</v>
+        <v>0.4420625986926303</v>
       </c>
       <c r="D53">
-        <v>0.3376863048175179</v>
+        <v>0.3379425986926303</v>
       </c>
       <c r="E53">
-        <v>0.42594</v>
+        <v>0.43488</v>
       </c>
       <c r="F53">
-        <v>0.45594</v>
+        <v>0.46488</v>
       </c>
       <c r="G53">
         <v>0.569</v>
@@ -5615,28 +5615,28 @@
         <v>0.397</v>
       </c>
       <c r="M53">
-        <v>0.022933782</v>
+        <v>0.023383464</v>
       </c>
       <c r="N53">
-        <v>0.374066218</v>
+        <v>0.3736165359999999</v>
       </c>
       <c r="O53">
-        <v>0.1122198654</v>
+        <v>0.1120849608</v>
       </c>
       <c r="P53">
-        <v>0.2618463526</v>
+        <v>0.2615315752</v>
       </c>
       <c r="Q53">
-        <v>0.4398463526</v>
+        <v>0.4395315752</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2740341206057357</v>
+        <v>0.2779637714426114</v>
       </c>
       <c r="T53">
-        <v>1.591349294979317</v>
+        <v>1.618748559700036</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>17.31070784574476</v>
+        <v>16.97780961794198</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1517318102924534</v>
+        <v>0.1512298014880964</v>
       </c>
       <c r="C54">
-        <v>0.4420625986926303</v>
+        <v>0.4333792819021129</v>
       </c>
       <c r="D54">
-        <v>0.3379425986926303</v>
+        <v>0.338199281902113</v>
       </c>
       <c r="E54">
-        <v>0.43488</v>
+        <v>0.44382</v>
       </c>
       <c r="F54">
-        <v>0.46488</v>
+        <v>0.47382</v>
       </c>
       <c r="G54">
         <v>0.569</v>
@@ -5697,28 +5697,28 @@
         <v>0.397</v>
       </c>
       <c r="M54">
-        <v>0.023383464</v>
+        <v>0.023833146</v>
       </c>
       <c r="N54">
-        <v>0.3736165359999999</v>
+        <v>0.3731668539999999</v>
       </c>
       <c r="O54">
-        <v>0.1120849608</v>
+        <v>0.1119500562</v>
       </c>
       <c r="P54">
-        <v>0.2615315752</v>
+        <v>0.2612167978</v>
       </c>
       <c r="Q54">
-        <v>0.4395315752</v>
+        <v>0.4392167977999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2779637714426114</v>
+        <v>0.2820606414640349</v>
       </c>
       <c r="T54">
-        <v>1.618748559700036</v>
+        <v>1.647313750579082</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>16.97780961794198</v>
+        <v>16.65747358741477</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1512298014880964</v>
+        <v>0.1507277926837393</v>
       </c>
       <c r="C55">
-        <v>0.4333792819021129</v>
+        <v>0.4246963553337933</v>
       </c>
       <c r="D55">
-        <v>0.338199281902113</v>
+        <v>0.3384563553337934</v>
       </c>
       <c r="E55">
-        <v>0.44382</v>
+        <v>0.45276</v>
       </c>
       <c r="F55">
-        <v>0.47382</v>
+        <v>0.48276</v>
       </c>
       <c r="G55">
         <v>0.569</v>
@@ -5779,28 +5779,28 @@
         <v>0.397</v>
       </c>
       <c r="M55">
-        <v>0.023833146</v>
+        <v>0.024282828</v>
       </c>
       <c r="N55">
-        <v>0.3731668539999999</v>
+        <v>0.372717172</v>
       </c>
       <c r="O55">
-        <v>0.1119500562</v>
+        <v>0.1118151516</v>
       </c>
       <c r="P55">
-        <v>0.2612167978</v>
+        <v>0.2609020204</v>
       </c>
       <c r="Q55">
-        <v>0.4392167977999999</v>
+        <v>0.4389020204</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2820606414640349</v>
+        <v>0.2863356362689986</v>
       </c>
       <c r="T55">
-        <v>1.647313750579082</v>
+        <v>1.677120906278957</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>16.65747358741477</v>
+        <v>16.3490018543145</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1507277926837393</v>
+        <v>0.1502257838793823</v>
       </c>
       <c r="C56">
-        <v>0.4246963553337933</v>
+        <v>0.4160138198782002</v>
       </c>
       <c r="D56">
-        <v>0.3384563553337934</v>
+        <v>0.3387138198782003</v>
       </c>
       <c r="E56">
-        <v>0.45276</v>
+        <v>0.4617</v>
       </c>
       <c r="F56">
-        <v>0.48276</v>
+        <v>0.4917</v>
       </c>
       <c r="G56">
         <v>0.569</v>
@@ -5861,28 +5861,28 @@
         <v>0.397</v>
       </c>
       <c r="M56">
-        <v>0.024282828</v>
+        <v>0.02473251</v>
       </c>
       <c r="N56">
-        <v>0.372717172</v>
+        <v>0.37226749</v>
       </c>
       <c r="O56">
-        <v>0.1118151516</v>
+        <v>0.111680247</v>
       </c>
       <c r="P56">
-        <v>0.2609020204</v>
+        <v>0.260587243</v>
       </c>
       <c r="Q56">
-        <v>0.4389020204</v>
+        <v>0.438587243</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2863356362689986</v>
+        <v>0.2908006308430717</v>
       </c>
       <c r="T56">
-        <v>1.677120906278957</v>
+        <v>1.708252824454382</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>16.3490018543145</v>
+        <v>16.05174727514514</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1502257838793823</v>
+        <v>0.1497237750750252</v>
       </c>
       <c r="C57">
-        <v>0.4160138198782002</v>
+        <v>0.407331676428574</v>
       </c>
       <c r="D57">
-        <v>0.3387138198782003</v>
+        <v>0.3389716764285742</v>
       </c>
       <c r="E57">
-        <v>0.4617</v>
+        <v>0.4706400000000001</v>
       </c>
       <c r="F57">
-        <v>0.4917</v>
+        <v>0.5006400000000001</v>
       </c>
       <c r="G57">
         <v>0.569</v>
@@ -5943,28 +5943,28 @@
         <v>0.397</v>
       </c>
       <c r="M57">
-        <v>0.02473251</v>
+        <v>0.025182192</v>
       </c>
       <c r="N57">
-        <v>0.37226749</v>
+        <v>0.371817808</v>
       </c>
       <c r="O57">
-        <v>0.111680247</v>
+        <v>0.1115453424</v>
       </c>
       <c r="P57">
-        <v>0.260587243</v>
+        <v>0.2602724656</v>
       </c>
       <c r="Q57">
-        <v>0.438587243</v>
+        <v>0.4382724656</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2908006308430717</v>
+        <v>0.2954685797159664</v>
       </c>
       <c r="T57">
-        <v>1.708252824454382</v>
+        <v>1.740799829819599</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>16.05174727514514</v>
+        <v>15.76510893094612</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1497237750750252</v>
+        <v>0.1492217662706681</v>
       </c>
       <c r="C58">
-        <v>0.407331676428574</v>
+        <v>0.3986499258808779</v>
       </c>
       <c r="D58">
-        <v>0.3389716764285742</v>
+        <v>0.339229925880878</v>
       </c>
       <c r="E58">
-        <v>0.4706400000000001</v>
+        <v>0.47958</v>
       </c>
       <c r="F58">
-        <v>0.5006400000000001</v>
+        <v>0.50958</v>
       </c>
       <c r="G58">
         <v>0.569</v>
@@ -6025,28 +6025,28 @@
         <v>0.397</v>
       </c>
       <c r="M58">
-        <v>0.025182192</v>
+        <v>0.025631874</v>
       </c>
       <c r="N58">
-        <v>0.371817808</v>
+        <v>0.371368126</v>
       </c>
       <c r="O58">
-        <v>0.1115453424</v>
+        <v>0.1114104378</v>
       </c>
       <c r="P58">
-        <v>0.2602724656</v>
+        <v>0.2599576882</v>
       </c>
       <c r="Q58">
-        <v>0.4382724656</v>
+        <v>0.4379576882</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2954685797159664</v>
+        <v>0.300353642489926</v>
       </c>
       <c r="T58">
-        <v>1.740799829819599</v>
+        <v>1.774860649387849</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>15.76510893094612</v>
+        <v>15.48852807250847</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1492217662706681</v>
+        <v>0.1487197574663111</v>
       </c>
       <c r="C59">
-        <v>0.3986499258808779</v>
+        <v>0.3899685691338066</v>
       </c>
       <c r="D59">
-        <v>0.339229925880878</v>
+        <v>0.3394885691338067</v>
       </c>
       <c r="E59">
-        <v>0.47958</v>
+        <v>0.4885200000000001</v>
       </c>
       <c r="F59">
-        <v>0.50958</v>
+        <v>0.5185200000000001</v>
       </c>
       <c r="G59">
         <v>0.569</v>
@@ -6107,28 +6107,28 @@
         <v>0.397</v>
       </c>
       <c r="M59">
-        <v>0.025631874</v>
+        <v>0.026081556</v>
       </c>
       <c r="N59">
-        <v>0.371368126</v>
+        <v>0.370918444</v>
       </c>
       <c r="O59">
-        <v>0.1114104378</v>
+        <v>0.1112755332</v>
       </c>
       <c r="P59">
-        <v>0.2599576882</v>
+        <v>0.2596429108</v>
       </c>
       <c r="Q59">
-        <v>0.4379576882</v>
+        <v>0.4376429108</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.300353642489926</v>
+        <v>0.3054713273007407</v>
       </c>
       <c r="T59">
-        <v>1.774860649387849</v>
+        <v>1.810543412745064</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>15.48852807250847</v>
+        <v>15.22148448505143</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1487197574663111</v>
+        <v>0.148217748661954</v>
       </c>
       <c r="C60">
-        <v>0.3899685691338067</v>
+        <v>0.3812876070887985</v>
       </c>
       <c r="D60">
-        <v>0.3394885691338067</v>
+        <v>0.3397476070887985</v>
       </c>
       <c r="E60">
-        <v>0.48852</v>
+        <v>0.4974599999999999</v>
       </c>
       <c r="F60">
-        <v>0.51852</v>
+        <v>0.5274599999999999</v>
       </c>
       <c r="G60">
         <v>0.569</v>
@@ -6189,28 +6189,28 @@
         <v>0.397</v>
       </c>
       <c r="M60">
-        <v>0.026081556</v>
+        <v>0.026531238</v>
       </c>
       <c r="N60">
-        <v>0.370918444</v>
+        <v>0.370468762</v>
       </c>
       <c r="O60">
-        <v>0.1112755332</v>
+        <v>0.1111406286</v>
       </c>
       <c r="P60">
-        <v>0.2596429108</v>
+        <v>0.2593281333999999</v>
       </c>
       <c r="Q60">
-        <v>0.4376429108</v>
+        <v>0.4373281333999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3054713273007407</v>
+        <v>0.3108386552730585</v>
       </c>
       <c r="T60">
-        <v>1.810543412745063</v>
+        <v>1.847966798705069</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>15.22148448505143</v>
+        <v>14.96349322259293</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.148217748661954</v>
+        <v>0.147715739857597</v>
       </c>
       <c r="C61">
-        <v>0.3812876070887985</v>
+        <v>0.3726070406500448</v>
       </c>
       <c r="D61">
-        <v>0.3397476070887985</v>
+        <v>0.3400070406500448</v>
       </c>
       <c r="E61">
-        <v>0.4974599999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="F61">
-        <v>0.5274599999999999</v>
+        <v>0.5364</v>
       </c>
       <c r="G61">
         <v>0.569</v>
@@ -6271,28 +6271,28 @@
         <v>0.397</v>
       </c>
       <c r="M61">
-        <v>0.026531238</v>
+        <v>0.02698092</v>
       </c>
       <c r="N61">
-        <v>0.370468762</v>
+        <v>0.3700190799999999</v>
       </c>
       <c r="O61">
-        <v>0.1111406286</v>
+        <v>0.111005724</v>
       </c>
       <c r="P61">
-        <v>0.2593281333999999</v>
+        <v>0.259013356</v>
       </c>
       <c r="Q61">
-        <v>0.4373281333999999</v>
+        <v>0.437013356</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3108386552730585</v>
+        <v>0.3164743496439924</v>
       </c>
       <c r="T61">
-        <v>1.847966798705069</v>
+        <v>1.887261353963074</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>14.96349322259293</v>
+        <v>14.71410166888305</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.147715739857597</v>
+        <v>0.1472137310532399</v>
       </c>
       <c r="C62">
-        <v>0.3726070406500448</v>
+        <v>0.3639268707245009</v>
       </c>
       <c r="D62">
-        <v>0.3400070406500448</v>
+        <v>0.340266870724501</v>
       </c>
       <c r="E62">
-        <v>0.5064</v>
+        <v>0.51534</v>
       </c>
       <c r="F62">
-        <v>0.5364</v>
+        <v>0.54534</v>
       </c>
       <c r="G62">
         <v>0.569</v>
@@ -6353,28 +6353,28 @@
         <v>0.397</v>
       </c>
       <c r="M62">
-        <v>0.02698092</v>
+        <v>0.027430602</v>
       </c>
       <c r="N62">
-        <v>0.3700190799999999</v>
+        <v>0.3695693979999999</v>
       </c>
       <c r="O62">
-        <v>0.111005724</v>
+        <v>0.1108708194</v>
       </c>
       <c r="P62">
-        <v>0.259013356</v>
+        <v>0.2586985786</v>
       </c>
       <c r="Q62">
-        <v>0.437013356</v>
+        <v>0.4366985785999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3164743496439924</v>
+        <v>0.3223990539826664</v>
       </c>
       <c r="T62">
-        <v>1.887261353963074</v>
+        <v>1.928571014618927</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>14.71410166888305</v>
+        <v>14.47288688742595</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1472137310532399</v>
+        <v>0.1467117222488828</v>
       </c>
       <c r="C63">
-        <v>0.3639268707245009</v>
+        <v>0.3552470982218968</v>
       </c>
       <c r="D63">
-        <v>0.340266870724501</v>
+        <v>0.3405270982218969</v>
       </c>
       <c r="E63">
-        <v>0.51534</v>
+        <v>0.52428</v>
       </c>
       <c r="F63">
-        <v>0.54534</v>
+        <v>0.55428</v>
       </c>
       <c r="G63">
         <v>0.569</v>
@@ -6435,28 +6435,28 @@
         <v>0.397</v>
       </c>
       <c r="M63">
-        <v>0.027430602</v>
+        <v>0.027880284</v>
       </c>
       <c r="N63">
-        <v>0.3695693979999999</v>
+        <v>0.369119716</v>
       </c>
       <c r="O63">
-        <v>0.1108708194</v>
+        <v>0.1107359148</v>
       </c>
       <c r="P63">
-        <v>0.2586985786</v>
+        <v>0.2583838012</v>
       </c>
       <c r="Q63">
-        <v>0.4366985785999999</v>
+        <v>0.4363838012</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3223990539826664</v>
+        <v>0.3286355848654811</v>
       </c>
       <c r="T63">
-        <v>1.928571014618927</v>
+        <v>1.972054867940876</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>14.47288688742595</v>
+        <v>14.23945322795134</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1467117222488828</v>
+        <v>0.1462097134445258</v>
       </c>
       <c r="C64">
-        <v>0.3552470982218968</v>
+        <v>0.3465677240547473</v>
       </c>
       <c r="D64">
-        <v>0.3405270982218969</v>
+        <v>0.3407877240547474</v>
       </c>
       <c r="E64">
-        <v>0.52428</v>
+        <v>0.53322</v>
       </c>
       <c r="F64">
-        <v>0.55428</v>
+        <v>0.5632200000000001</v>
       </c>
       <c r="G64">
         <v>0.569</v>
@@ -6517,28 +6517,28 @@
         <v>0.397</v>
       </c>
       <c r="M64">
-        <v>0.027880284</v>
+        <v>0.028329966</v>
       </c>
       <c r="N64">
-        <v>0.369119716</v>
+        <v>0.368670034</v>
       </c>
       <c r="O64">
-        <v>0.1107359148</v>
+        <v>0.1106010102</v>
       </c>
       <c r="P64">
-        <v>0.2583838012</v>
+        <v>0.2580690238</v>
       </c>
       <c r="Q64">
-        <v>0.4363838012</v>
+        <v>0.4360690238</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3286355848654811</v>
+        <v>0.3352092255257454</v>
       </c>
       <c r="T64">
-        <v>1.972054867940876</v>
+        <v>2.01788919982077</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>14.23945322795134</v>
+        <v>14.013430160841</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1462097134445258</v>
+        <v>0.1457077046401687</v>
       </c>
       <c r="C65">
-        <v>0.3465677240547473</v>
+        <v>0.3378887491383631</v>
       </c>
       <c r="D65">
-        <v>0.3407877240547474</v>
+        <v>0.3410487491383632</v>
       </c>
       <c r="E65">
-        <v>0.53322</v>
+        <v>0.54216</v>
       </c>
       <c r="F65">
-        <v>0.5632200000000001</v>
+        <v>0.57216</v>
       </c>
       <c r="G65">
         <v>0.569</v>
@@ -6599,28 +6599,28 @@
         <v>0.397</v>
       </c>
       <c r="M65">
-        <v>0.028329966</v>
+        <v>0.028779648</v>
       </c>
       <c r="N65">
-        <v>0.368670034</v>
+        <v>0.368220352</v>
       </c>
       <c r="O65">
-        <v>0.1106010102</v>
+        <v>0.1104661056</v>
       </c>
       <c r="P65">
-        <v>0.2580690238</v>
+        <v>0.2577542464</v>
       </c>
       <c r="Q65">
-        <v>0.4360690238</v>
+        <v>0.4357542464</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3352092255257454</v>
+        <v>0.3421480684449131</v>
       </c>
       <c r="T65">
-        <v>2.01788919982077</v>
+        <v>2.066269883471767</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>14.013430160841</v>
+        <v>13.79447031457786</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1457077046401687</v>
+        <v>0.1452056958358116</v>
       </c>
       <c r="C66">
-        <v>0.3378887491383631</v>
+        <v>0.3292101743908613</v>
       </c>
       <c r="D66">
-        <v>0.3410487491383632</v>
+        <v>0.3413101743908614</v>
       </c>
       <c r="E66">
-        <v>0.54216</v>
+        <v>0.5511</v>
       </c>
       <c r="F66">
-        <v>0.57216</v>
+        <v>0.5811000000000001</v>
       </c>
       <c r="G66">
         <v>0.569</v>
@@ -6681,28 +6681,28 @@
         <v>0.397</v>
       </c>
       <c r="M66">
-        <v>0.028779648</v>
+        <v>0.02922933</v>
       </c>
       <c r="N66">
-        <v>0.368220352</v>
+        <v>0.36777067</v>
       </c>
       <c r="O66">
-        <v>0.1104661056</v>
+        <v>0.110331201</v>
       </c>
       <c r="P66">
-        <v>0.2577542464</v>
+        <v>0.257439469</v>
       </c>
       <c r="Q66">
-        <v>0.4357542464</v>
+        <v>0.435439469</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3421480684449131</v>
+        <v>0.3494834166737475</v>
       </c>
       <c r="T66">
-        <v>2.066269883471767</v>
+        <v>2.117415177617108</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>13.79447031457786</v>
+        <v>13.58224769435358</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1452056958358116</v>
+        <v>0.1447036870314546</v>
       </c>
       <c r="C67">
-        <v>0.3292101743908613</v>
+        <v>0.3205320007331763</v>
       </c>
       <c r="D67">
-        <v>0.3413101743908614</v>
+        <v>0.3415720007331763</v>
       </c>
       <c r="E67">
-        <v>0.5511</v>
+        <v>0.56004</v>
       </c>
       <c r="F67">
-        <v>0.5811000000000001</v>
+        <v>0.59004</v>
       </c>
       <c r="G67">
         <v>0.569</v>
@@ -6763,28 +6763,28 @@
         <v>0.397</v>
       </c>
       <c r="M67">
-        <v>0.02922933</v>
+        <v>0.029679012</v>
       </c>
       <c r="N67">
-        <v>0.36777067</v>
+        <v>0.367320988</v>
       </c>
       <c r="O67">
-        <v>0.110331201</v>
+        <v>0.1101962964</v>
       </c>
       <c r="P67">
-        <v>0.257439469</v>
+        <v>0.2571246916</v>
       </c>
       <c r="Q67">
-        <v>0.435439469</v>
+        <v>0.4351246915999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3494834166737475</v>
+        <v>0.3572502559748665</v>
       </c>
       <c r="T67">
-        <v>2.117415177617108</v>
+        <v>2.171569018476881</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>13.58224769435358</v>
+        <v>13.37645606262095</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1447036870314546</v>
+        <v>0.1442016782270975</v>
       </c>
       <c r="C68">
-        <v>0.3205320007331763</v>
+        <v>0.3118542290890702</v>
       </c>
       <c r="D68">
-        <v>0.3415720007331763</v>
+        <v>0.3418342290890704</v>
       </c>
       <c r="E68">
-        <v>0.56004</v>
+        <v>0.56898</v>
       </c>
       <c r="F68">
-        <v>0.59004</v>
+        <v>0.5989800000000001</v>
       </c>
       <c r="G68">
         <v>0.569</v>
@@ -6845,28 +6845,28 @@
         <v>0.397</v>
       </c>
       <c r="M68">
-        <v>0.029679012</v>
+        <v>0.030128694</v>
       </c>
       <c r="N68">
-        <v>0.367320988</v>
+        <v>0.366871306</v>
       </c>
       <c r="O68">
-        <v>0.1101962964</v>
+        <v>0.1100613918</v>
       </c>
       <c r="P68">
-        <v>0.2571246916</v>
+        <v>0.2568099142</v>
       </c>
       <c r="Q68">
-        <v>0.4351246915999999</v>
+        <v>0.4348099142</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3572502559748665</v>
+        <v>0.3654878128093865</v>
       </c>
       <c r="T68">
-        <v>2.171569018476881</v>
+        <v>2.229004910297852</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>13.37645606262095</v>
+        <v>13.17680746467138</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1442016782270975</v>
+        <v>0.1436996694227405</v>
       </c>
       <c r="C69">
-        <v>0.3118542290890702</v>
+        <v>0.3031768603851448</v>
       </c>
       <c r="D69">
-        <v>0.3418342290890704</v>
+        <v>0.3420968603851449</v>
       </c>
       <c r="E69">
-        <v>0.56898</v>
+        <v>0.57792</v>
       </c>
       <c r="F69">
-        <v>0.5989800000000001</v>
+        <v>0.60792</v>
       </c>
       <c r="G69">
         <v>0.569</v>
@@ -6927,28 +6927,28 @@
         <v>0.397</v>
       </c>
       <c r="M69">
-        <v>0.030128694</v>
+        <v>0.030578376</v>
       </c>
       <c r="N69">
-        <v>0.366871306</v>
+        <v>0.3664216239999999</v>
       </c>
       <c r="O69">
-        <v>0.1100613918</v>
+        <v>0.1099264872</v>
       </c>
       <c r="P69">
-        <v>0.2568099142</v>
+        <v>0.2564951368</v>
       </c>
       <c r="Q69">
-        <v>0.4348099142</v>
+        <v>0.4344951368</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3654878128093865</v>
+        <v>0.374240216946064</v>
       </c>
       <c r="T69">
-        <v>2.229004910297852</v>
+        <v>2.290030545357634</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>13.17680746467138</v>
+        <v>12.98303088430857</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1436996694227405</v>
+        <v>0.1439221606183834</v>
       </c>
       <c r="C70">
-        <v>0.3031768603851448</v>
+        <v>0.2941204119502344</v>
       </c>
       <c r="D70">
-        <v>0.3420968603851449</v>
+        <v>0.3419804119502346</v>
       </c>
       <c r="E70">
-        <v>0.57792</v>
+        <v>0.58686</v>
       </c>
       <c r="F70">
-        <v>0.60792</v>
+        <v>0.6168600000000001</v>
       </c>
       <c r="G70">
         <v>0.569</v>
@@ -7009,45 +7009,45 @@
         <v>0.397</v>
       </c>
       <c r="M70">
-        <v>0.030578376</v>
+        <v>0.03195334800000001</v>
       </c>
       <c r="N70">
-        <v>0.3664216239999999</v>
+        <v>0.365046652</v>
       </c>
       <c r="O70">
-        <v>0.1099264872</v>
+        <v>0.1095139956</v>
       </c>
       <c r="P70">
-        <v>0.2564951368</v>
+        <v>0.2555326564</v>
       </c>
       <c r="Q70">
-        <v>0.4344951368</v>
+        <v>0.4335326564</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.374240216946064</v>
+        <v>0.3835572923173659</v>
       </c>
       <c r="T70">
-        <v>2.290030545357634</v>
+        <v>2.354993318163208</v>
       </c>
       <c r="U70">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V70">
         <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y70">
-        <v>12.98303088430857</v>
+        <v>12.42436316845421</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1439221606183834</v>
+        <v>0.1434306518140263</v>
       </c>
       <c r="C71">
-        <v>0.2941204119502344</v>
+        <v>0.2854377659791622</v>
       </c>
       <c r="D71">
-        <v>0.3419804119502346</v>
+        <v>0.3422377659791622</v>
       </c>
       <c r="E71">
-        <v>0.58686</v>
+        <v>0.5958</v>
       </c>
       <c r="F71">
-        <v>0.6168600000000001</v>
+        <v>0.6258</v>
       </c>
       <c r="G71">
         <v>0.569</v>
@@ -7091,28 +7091,28 @@
         <v>0.397</v>
       </c>
       <c r="M71">
-        <v>0.03195334800000001</v>
+        <v>0.03241644</v>
       </c>
       <c r="N71">
-        <v>0.365046652</v>
+        <v>0.36458356</v>
       </c>
       <c r="O71">
-        <v>0.1095139956</v>
+        <v>0.109375068</v>
       </c>
       <c r="P71">
-        <v>0.2555326564</v>
+        <v>0.255208492</v>
       </c>
       <c r="Q71">
-        <v>0.4335326564</v>
+        <v>0.4332084919999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3835572923173659</v>
+        <v>0.3934955060467545</v>
       </c>
       <c r="T71">
-        <v>2.354993318163208</v>
+        <v>2.424286942489153</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>12.42436316845421</v>
+        <v>12.24687226604772</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1434306518140263</v>
+        <v>0.1429391430096693</v>
       </c>
       <c r="C72">
-        <v>0.2854377659791622</v>
+        <v>0.2767555076383338</v>
       </c>
       <c r="D72">
-        <v>0.3422377659791622</v>
+        <v>0.3424955076383339</v>
       </c>
       <c r="E72">
-        <v>0.5958</v>
+        <v>0.6047400000000001</v>
       </c>
       <c r="F72">
-        <v>0.6258</v>
+        <v>0.6347400000000001</v>
       </c>
       <c r="G72">
         <v>0.569</v>
@@ -7173,28 +7173,28 @@
         <v>0.397</v>
       </c>
       <c r="M72">
-        <v>0.03241644</v>
+        <v>0.032879532</v>
       </c>
       <c r="N72">
-        <v>0.36458356</v>
+        <v>0.364120468</v>
       </c>
       <c r="O72">
-        <v>0.109375068</v>
+        <v>0.1092361404</v>
       </c>
       <c r="P72">
-        <v>0.255208492</v>
+        <v>0.2548843276</v>
       </c>
       <c r="Q72">
-        <v>0.4332084919999999</v>
+        <v>0.4328843276</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3934955060467545</v>
+        <v>0.4041191138264459</v>
       </c>
       <c r="T72">
-        <v>2.424286942489153</v>
+        <v>2.498359437458268</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>12.24687226604772</v>
+        <v>12.07438110737099</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1429391430096693</v>
+        <v>0.1424476342053122</v>
       </c>
       <c r="C73">
-        <v>0.2767555076383339</v>
+        <v>0.268073637804191</v>
       </c>
       <c r="D73">
-        <v>0.3424955076383339</v>
+        <v>0.3427536378041912</v>
       </c>
       <c r="E73">
-        <v>0.6047399999999999</v>
+        <v>0.61368</v>
       </c>
       <c r="F73">
-        <v>0.63474</v>
+        <v>0.64368</v>
       </c>
       <c r="G73">
         <v>0.569</v>
@@ -7255,28 +7255,28 @@
         <v>0.397</v>
       </c>
       <c r="M73">
-        <v>0.032879532</v>
+        <v>0.033342624</v>
       </c>
       <c r="N73">
-        <v>0.364120468</v>
+        <v>0.363657376</v>
       </c>
       <c r="O73">
-        <v>0.1092361404</v>
+        <v>0.1090972128</v>
       </c>
       <c r="P73">
-        <v>0.2548843276</v>
+        <v>0.2545601632</v>
       </c>
       <c r="Q73">
-        <v>0.4328843276</v>
+        <v>0.4325601632</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4041191138264458</v>
+        <v>0.4155015507332579</v>
       </c>
       <c r="T73">
-        <v>2.498359437458267</v>
+        <v>2.577722824925175</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>12.07438110737099</v>
+        <v>11.90668136976862</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1424476342053122</v>
+        <v>0.1419561254009551</v>
       </c>
       <c r="C74">
-        <v>0.268073637804191</v>
+        <v>0.2593921573558193</v>
       </c>
       <c r="D74">
-        <v>0.3427536378041912</v>
+        <v>0.3430121573558193</v>
       </c>
       <c r="E74">
-        <v>0.61368</v>
+        <v>0.62262</v>
       </c>
       <c r="F74">
-        <v>0.64368</v>
+        <v>0.65262</v>
       </c>
       <c r="G74">
         <v>0.569</v>
@@ -7337,28 +7337,28 @@
         <v>0.397</v>
       </c>
       <c r="M74">
-        <v>0.033342624</v>
+        <v>0.033805716</v>
       </c>
       <c r="N74">
-        <v>0.363657376</v>
+        <v>0.363194284</v>
       </c>
       <c r="O74">
-        <v>0.1090972128</v>
+        <v>0.1089582852</v>
       </c>
       <c r="P74">
-        <v>0.2545601632</v>
+        <v>0.2542359988</v>
       </c>
       <c r="Q74">
-        <v>0.4325601632</v>
+        <v>0.4322359988</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4155015507332579</v>
+        <v>0.4277271311146487</v>
       </c>
       <c r="T74">
-        <v>2.577722824925175</v>
+        <v>2.662964981834076</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>11.90668136976862</v>
+        <v>11.74357614552521</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1419561254009551</v>
+        <v>0.1414646165965981</v>
       </c>
       <c r="C75">
-        <v>0.2593921573558193</v>
+        <v>0.2507110671749578</v>
       </c>
       <c r="D75">
-        <v>0.3430121573558193</v>
+        <v>0.3432710671749579</v>
       </c>
       <c r="E75">
-        <v>0.62262</v>
+        <v>0.63156</v>
       </c>
       <c r="F75">
-        <v>0.65262</v>
+        <v>0.66156</v>
       </c>
       <c r="G75">
         <v>0.569</v>
@@ -7419,28 +7419,28 @@
         <v>0.397</v>
       </c>
       <c r="M75">
-        <v>0.033805716</v>
+        <v>0.034268808</v>
       </c>
       <c r="N75">
-        <v>0.363194284</v>
+        <v>0.362731192</v>
       </c>
       <c r="O75">
-        <v>0.1089582852</v>
+        <v>0.1088193576</v>
       </c>
       <c r="P75">
-        <v>0.2542359988</v>
+        <v>0.2539118344</v>
       </c>
       <c r="Q75">
-        <v>0.4322359988</v>
+        <v>0.4319118344</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4277271311146487</v>
+        <v>0.4408931407561465</v>
       </c>
       <c r="T75">
-        <v>2.662964981834076</v>
+        <v>2.75476422773597</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>11.74357614552521</v>
+        <v>11.58487917058568</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1414646165965981</v>
+        <v>0.140973107792241</v>
       </c>
       <c r="C76">
-        <v>0.2507110671749578</v>
+        <v>0.2420303681460108</v>
       </c>
       <c r="D76">
-        <v>0.3432710671749579</v>
+        <v>0.3435303681460108</v>
       </c>
       <c r="E76">
-        <v>0.63156</v>
+        <v>0.6405</v>
       </c>
       <c r="F76">
-        <v>0.66156</v>
+        <v>0.6705</v>
       </c>
       <c r="G76">
         <v>0.569</v>
@@ -7501,28 +7501,28 @@
         <v>0.397</v>
       </c>
       <c r="M76">
-        <v>0.034268808</v>
+        <v>0.0347319</v>
       </c>
       <c r="N76">
-        <v>0.362731192</v>
+        <v>0.3622681</v>
       </c>
       <c r="O76">
-        <v>0.1088193576</v>
+        <v>0.10868043</v>
       </c>
       <c r="P76">
-        <v>0.2539118344</v>
+        <v>0.25358767</v>
       </c>
       <c r="Q76">
-        <v>0.4319118344</v>
+        <v>0.43158767</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4408931407561465</v>
+        <v>0.4551124311689641</v>
       </c>
       <c r="T76">
-        <v>2.75476422773597</v>
+        <v>2.853907413310015</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>11.58487917058568</v>
+        <v>11.43041411497787</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.140973107792241</v>
+        <v>0.140481598987884</v>
       </c>
       <c r="C77">
-        <v>0.2420303681460108</v>
+        <v>0.2333500611560559</v>
       </c>
       <c r="D77">
-        <v>0.3435303681460108</v>
+        <v>0.343790061156056</v>
       </c>
       <c r="E77">
-        <v>0.6405</v>
+        <v>0.64944</v>
       </c>
       <c r="F77">
-        <v>0.6705</v>
+        <v>0.67944</v>
       </c>
       <c r="G77">
         <v>0.569</v>
@@ -7583,28 +7583,28 @@
         <v>0.397</v>
       </c>
       <c r="M77">
-        <v>0.0347319</v>
+        <v>0.035194992</v>
       </c>
       <c r="N77">
-        <v>0.3622681</v>
+        <v>0.361805008</v>
       </c>
       <c r="O77">
-        <v>0.10868043</v>
+        <v>0.1085415024</v>
       </c>
       <c r="P77">
-        <v>0.25358767</v>
+        <v>0.2532635056</v>
       </c>
       <c r="Q77">
-        <v>0.43158767</v>
+        <v>0.4312635056</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4551124311689641</v>
+        <v>0.4705166624495166</v>
       </c>
       <c r="T77">
-        <v>2.853907413310015</v>
+        <v>2.961312531015231</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>11.43041411497787</v>
+        <v>11.28001392925448</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.140481598987884</v>
+        <v>0.1399900901835269</v>
       </c>
       <c r="C78">
-        <v>0.2333500611560559</v>
+        <v>0.224670147094856</v>
       </c>
       <c r="D78">
-        <v>0.343790061156056</v>
+        <v>0.344050147094856</v>
       </c>
       <c r="E78">
-        <v>0.64944</v>
+        <v>0.65838</v>
       </c>
       <c r="F78">
-        <v>0.67944</v>
+        <v>0.68838</v>
       </c>
       <c r="G78">
         <v>0.569</v>
@@ -7665,28 +7665,28 @@
         <v>0.397</v>
       </c>
       <c r="M78">
-        <v>0.035194992</v>
+        <v>0.035658084</v>
       </c>
       <c r="N78">
-        <v>0.361805008</v>
+        <v>0.361341916</v>
       </c>
       <c r="O78">
-        <v>0.1085415024</v>
+        <v>0.1084025748</v>
       </c>
       <c r="P78">
-        <v>0.2532635056</v>
+        <v>0.2529393412</v>
       </c>
       <c r="Q78">
-        <v>0.4312635056</v>
+        <v>0.4309393412</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4705166624495166</v>
+        <v>0.4872603921022909</v>
       </c>
       <c r="T78">
-        <v>2.961312531015231</v>
+        <v>3.078057224173074</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>11.28001392925448</v>
+        <v>11.13352024186156</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1399900901835269</v>
+        <v>0.1394985813791698</v>
       </c>
       <c r="C79">
-        <v>0.224670147094856</v>
+        <v>0.2159906268548676</v>
       </c>
       <c r="D79">
-        <v>0.344050147094856</v>
+        <v>0.3443106268548677</v>
       </c>
       <c r="E79">
-        <v>0.65838</v>
+        <v>0.66732</v>
       </c>
       <c r="F79">
-        <v>0.68838</v>
+        <v>0.6973200000000001</v>
       </c>
       <c r="G79">
         <v>0.569</v>
@@ -7747,28 +7747,28 @@
         <v>0.397</v>
       </c>
       <c r="M79">
-        <v>0.035658084</v>
+        <v>0.036121176</v>
       </c>
       <c r="N79">
-        <v>0.361341916</v>
+        <v>0.3608788239999999</v>
       </c>
       <c r="O79">
-        <v>0.1084025748</v>
+        <v>0.1082636472</v>
       </c>
       <c r="P79">
-        <v>0.2529393412</v>
+        <v>0.2526151768</v>
       </c>
       <c r="Q79">
-        <v>0.4309393412</v>
+        <v>0.4306151767999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4872603921022909</v>
+        <v>0.5055262789962266</v>
       </c>
       <c r="T79">
-        <v>3.078057224173074</v>
+        <v>3.205415071254357</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>11.13352024186156</v>
+        <v>10.99078280286334</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1394985813791698</v>
+        <v>0.1390070725748128</v>
       </c>
       <c r="C80">
-        <v>0.2159906268548676</v>
+        <v>0.207311501331253</v>
       </c>
       <c r="D80">
-        <v>0.3443106268548677</v>
+        <v>0.344571501331253</v>
       </c>
       <c r="E80">
-        <v>0.66732</v>
+        <v>0.67626</v>
       </c>
       <c r="F80">
-        <v>0.6973200000000001</v>
+        <v>0.70626</v>
       </c>
       <c r="G80">
         <v>0.569</v>
@@ -7829,28 +7829,28 @@
         <v>0.397</v>
       </c>
       <c r="M80">
-        <v>0.036121176</v>
+        <v>0.036584268</v>
       </c>
       <c r="N80">
-        <v>0.3608788239999999</v>
+        <v>0.360415732</v>
       </c>
       <c r="O80">
-        <v>0.1082636472</v>
+        <v>0.1081247196</v>
       </c>
       <c r="P80">
-        <v>0.2526151768</v>
+        <v>0.2522910124</v>
       </c>
       <c r="Q80">
-        <v>0.4306151767999999</v>
+        <v>0.4302910124</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5055262789962266</v>
+        <v>0.5255317741657752</v>
       </c>
       <c r="T80">
-        <v>3.205415071254357</v>
+        <v>3.344902237105287</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>10.99078280286334</v>
+        <v>10.8516589699157</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1390070725748128</v>
+        <v>0.1385155637704557</v>
       </c>
       <c r="C81">
-        <v>0.207311501331253</v>
+        <v>0.1986327714218885</v>
       </c>
       <c r="D81">
-        <v>0.344571501331253</v>
+        <v>0.3448327714218887</v>
       </c>
       <c r="E81">
-        <v>0.67626</v>
+        <v>0.6852</v>
       </c>
       <c r="F81">
-        <v>0.70626</v>
+        <v>0.7152000000000001</v>
       </c>
       <c r="G81">
         <v>0.569</v>
@@ -7911,28 +7911,28 @@
         <v>0.397</v>
       </c>
       <c r="M81">
-        <v>0.036584268</v>
+        <v>0.03704736</v>
       </c>
       <c r="N81">
-        <v>0.360415732</v>
+        <v>0.3599526399999999</v>
       </c>
       <c r="O81">
-        <v>0.1081247196</v>
+        <v>0.107985792</v>
       </c>
       <c r="P81">
-        <v>0.2522910124</v>
+        <v>0.251966848</v>
       </c>
       <c r="Q81">
-        <v>0.4302910124</v>
+        <v>0.429966848</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5255317741657752</v>
+        <v>0.5475378188522787</v>
       </c>
       <c r="T81">
-        <v>3.344902237105287</v>
+        <v>3.49833811954131</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>10.8516589699157</v>
+        <v>10.71601323279175</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1385155637704557</v>
+        <v>0.1380240549660986</v>
       </c>
       <c r="C82">
-        <v>0.1986327714218885</v>
+        <v>0.1899544380273765</v>
       </c>
       <c r="D82">
-        <v>0.3448327714218887</v>
+        <v>0.3450944380273767</v>
       </c>
       <c r="E82">
-        <v>0.6852</v>
+        <v>0.69414</v>
       </c>
       <c r="F82">
-        <v>0.7152000000000001</v>
+        <v>0.72414</v>
       </c>
       <c r="G82">
         <v>0.569</v>
@@ -7993,28 +7993,28 @@
         <v>0.397</v>
       </c>
       <c r="M82">
-        <v>0.03704736</v>
+        <v>0.037510452</v>
       </c>
       <c r="N82">
-        <v>0.3599526399999999</v>
+        <v>0.359489548</v>
       </c>
       <c r="O82">
-        <v>0.107985792</v>
+        <v>0.1078468644</v>
       </c>
       <c r="P82">
-        <v>0.251966848</v>
+        <v>0.2516426836</v>
       </c>
       <c r="Q82">
-        <v>0.429966848</v>
+        <v>0.4296426836</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5475378188522787</v>
+        <v>0.5718602892952561</v>
       </c>
       <c r="T82">
-        <v>3.49833811954131</v>
+        <v>3.667925147496913</v>
       </c>
       <c r="U82">
         <v>0.0518</v>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>10.71601323279175</v>
+        <v>10.58371677312766</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1380240549660986</v>
+        <v>0.1375325461617416</v>
       </c>
       <c r="C83">
-        <v>0.1899544380273765</v>
+        <v>0.1812765020510546</v>
       </c>
       <c r="D83">
-        <v>0.3450944380273767</v>
+        <v>0.3453565020510548</v>
       </c>
       <c r="E83">
-        <v>0.69414</v>
+        <v>0.70308</v>
       </c>
       <c r="F83">
-        <v>0.72414</v>
+        <v>0.7330800000000001</v>
       </c>
       <c r="G83">
         <v>0.569</v>
@@ -8075,28 +8075,28 @@
         <v>0.397</v>
       </c>
       <c r="M83">
-        <v>0.037510452</v>
+        <v>0.037973544</v>
       </c>
       <c r="N83">
-        <v>0.359489548</v>
+        <v>0.3590264559999999</v>
       </c>
       <c r="O83">
-        <v>0.1078468644</v>
+        <v>0.1077079368</v>
       </c>
       <c r="P83">
-        <v>0.2516426836</v>
+        <v>0.2513185192</v>
       </c>
       <c r="Q83">
-        <v>0.4296426836</v>
+        <v>0.4293185192</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5718602892952561</v>
+        <v>0.5988852564541201</v>
       </c>
       <c r="T83">
-        <v>3.667925147496913</v>
+        <v>3.856355178558696</v>
       </c>
       <c r="U83">
         <v>0.0518</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>10.58371677312766</v>
+        <v>10.4546470563822</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1375325461617416</v>
+        <v>0.1370410373573845</v>
       </c>
       <c r="C84">
-        <v>0.1812765020510546</v>
+        <v>0.1725989643990067</v>
       </c>
       <c r="D84">
-        <v>0.3453565020510548</v>
+        <v>0.3456189643990069</v>
       </c>
       <c r="E84">
-        <v>0.70308</v>
+        <v>0.7120200000000001</v>
       </c>
       <c r="F84">
-        <v>0.7330800000000001</v>
+        <v>0.7420200000000001</v>
       </c>
       <c r="G84">
         <v>0.569</v>
@@ -8157,28 +8157,28 @@
         <v>0.397</v>
       </c>
       <c r="M84">
-        <v>0.037973544</v>
+        <v>0.038436636</v>
       </c>
       <c r="N84">
-        <v>0.3590264559999999</v>
+        <v>0.3585633639999999</v>
       </c>
       <c r="O84">
-        <v>0.1077079368</v>
+        <v>0.1075690092</v>
       </c>
       <c r="P84">
-        <v>0.2513185192</v>
+        <v>0.2509943548</v>
       </c>
       <c r="Q84">
-        <v>0.4293185192</v>
+        <v>0.4289943548</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5988852564541201</v>
+        <v>0.6290896315140267</v>
       </c>
       <c r="T84">
-        <v>3.856355178558696</v>
+        <v>4.066953448568922</v>
       </c>
       <c r="U84">
         <v>0.0518</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>10.4546470563822</v>
+        <v>10.32868745329326</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1370410373573845</v>
+        <v>0.1365495285530275</v>
       </c>
       <c r="C85">
-        <v>0.1725989643990067</v>
+        <v>0.1639218259800732</v>
       </c>
       <c r="D85">
-        <v>0.3456189643990069</v>
+        <v>0.3458818259800733</v>
       </c>
       <c r="E85">
-        <v>0.7120200000000001</v>
+        <v>0.72096</v>
       </c>
       <c r="F85">
-        <v>0.7420200000000001</v>
+        <v>0.7509600000000001</v>
       </c>
       <c r="G85">
         <v>0.569</v>
@@ -8239,28 +8239,28 @@
         <v>0.397</v>
       </c>
       <c r="M85">
-        <v>0.038436636</v>
+        <v>0.038899728</v>
       </c>
       <c r="N85">
-        <v>0.3585633639999999</v>
+        <v>0.3581002719999999</v>
       </c>
       <c r="O85">
-        <v>0.1075690092</v>
+        <v>0.1074300816</v>
       </c>
       <c r="P85">
-        <v>0.2509943548</v>
+        <v>0.2506701903999999</v>
       </c>
       <c r="Q85">
-        <v>0.4289943548</v>
+        <v>0.4286701903999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6290896315140267</v>
+        <v>0.663069553456422</v>
       </c>
       <c r="T85">
-        <v>4.066953448568922</v>
+        <v>4.303876502330429</v>
       </c>
       <c r="U85">
         <v>0.0518</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>10.32868745329326</v>
+        <v>10.2057268883731</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1365495285530275</v>
+        <v>0.1360580197486704</v>
       </c>
       <c r="C86">
-        <v>0.1639218259800733</v>
+        <v>0.1552450877058612</v>
       </c>
       <c r="D86">
-        <v>0.3458818259800733</v>
+        <v>0.3461450877058613</v>
       </c>
       <c r="E86">
-        <v>0.7209599999999999</v>
+        <v>0.7299</v>
       </c>
       <c r="F86">
-        <v>0.75096</v>
+        <v>0.7599</v>
       </c>
       <c r="G86">
         <v>0.569</v>
@@ -8321,28 +8321,28 @@
         <v>0.397</v>
       </c>
       <c r="M86">
-        <v>0.03889972799999999</v>
+        <v>0.03936282</v>
       </c>
       <c r="N86">
-        <v>0.3581002719999999</v>
+        <v>0.3576371799999999</v>
       </c>
       <c r="O86">
-        <v>0.1074300816</v>
+        <v>0.107291154</v>
       </c>
       <c r="P86">
-        <v>0.2506701903999999</v>
+        <v>0.2503460259999999</v>
       </c>
       <c r="Q86">
-        <v>0.4286701903999999</v>
+        <v>0.4283460259999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6630695534564215</v>
+        <v>0.7015801316578026</v>
       </c>
       <c r="T86">
-        <v>4.303876502330425</v>
+        <v>4.572389296593465</v>
       </c>
       <c r="U86">
         <v>0.0518</v>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>10.2057268883731</v>
+        <v>10.08565951321577</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1360580197486704</v>
+        <v>0.1355665109443134</v>
       </c>
       <c r="C87">
-        <v>0.1552450877058612</v>
+        <v>0.1465687504907556</v>
       </c>
       <c r="D87">
-        <v>0.3461450877058613</v>
+        <v>0.3464087504907556</v>
       </c>
       <c r="E87">
-        <v>0.7299</v>
+        <v>0.7388399999999999</v>
       </c>
       <c r="F87">
-        <v>0.7599</v>
+        <v>0.76884</v>
       </c>
       <c r="G87">
         <v>0.569</v>
@@ -8403,28 +8403,28 @@
         <v>0.397</v>
       </c>
       <c r="M87">
-        <v>0.03936282</v>
+        <v>0.039825912</v>
       </c>
       <c r="N87">
-        <v>0.3576371799999999</v>
+        <v>0.3571740879999999</v>
       </c>
       <c r="O87">
-        <v>0.107291154</v>
+        <v>0.1071522264</v>
       </c>
       <c r="P87">
-        <v>0.2503460259999999</v>
+        <v>0.2500218616</v>
       </c>
       <c r="Q87">
-        <v>0.4283460259999999</v>
+        <v>0.4280218615999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7015801316578026</v>
+        <v>0.7455922210308096</v>
       </c>
       <c r="T87">
-        <v>4.572389296593465</v>
+        <v>4.87926106146551</v>
       </c>
       <c r="U87">
         <v>0.0518</v>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>10.08565951321577</v>
+        <v>9.968384402596982</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1355665109443134</v>
+        <v>0.1350750021399563</v>
       </c>
       <c r="C88">
-        <v>0.1465687504907556</v>
+        <v>0.1378928152519291</v>
       </c>
       <c r="D88">
-        <v>0.3464087504907556</v>
+        <v>0.3466728152519292</v>
       </c>
       <c r="E88">
-        <v>0.7388399999999999</v>
+        <v>0.74778</v>
       </c>
       <c r="F88">
-        <v>0.76884</v>
+        <v>0.77778</v>
       </c>
       <c r="G88">
         <v>0.569</v>
@@ -8485,28 +8485,28 @@
         <v>0.397</v>
       </c>
       <c r="M88">
-        <v>0.039825912</v>
+        <v>0.040289004</v>
       </c>
       <c r="N88">
-        <v>0.3571740879999999</v>
+        <v>0.3567109959999999</v>
       </c>
       <c r="O88">
-        <v>0.1071522264</v>
+        <v>0.1070132988</v>
       </c>
       <c r="P88">
-        <v>0.2500218616</v>
+        <v>0.2496976972</v>
       </c>
       <c r="Q88">
-        <v>0.4280218615999999</v>
+        <v>0.4276976971999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7455922210308096</v>
+        <v>0.7963754010765867</v>
       </c>
       <c r="T88">
-        <v>4.87926106146551</v>
+        <v>5.2333438670871</v>
       </c>
       <c r="U88">
         <v>0.0518</v>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>9.968384402596982</v>
+        <v>9.853805271532648</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1350750021399563</v>
+        <v>0.1356306933355992</v>
       </c>
       <c r="C89">
-        <v>0.1378928152519291</v>
+        <v>0.1286542979771489</v>
       </c>
       <c r="D89">
-        <v>0.3466728152519292</v>
+        <v>0.3463742979771489</v>
       </c>
       <c r="E89">
-        <v>0.74778</v>
+        <v>0.7567199999999999</v>
       </c>
       <c r="F89">
-        <v>0.77778</v>
+        <v>0.78672</v>
       </c>
       <c r="G89">
         <v>0.569</v>
@@ -8567,45 +8567,45 @@
         <v>0.397</v>
       </c>
       <c r="M89">
-        <v>0.040289004</v>
+        <v>0.04208952</v>
       </c>
       <c r="N89">
-        <v>0.3567109959999999</v>
+        <v>0.35491048</v>
       </c>
       <c r="O89">
-        <v>0.1070132988</v>
+        <v>0.106473144</v>
       </c>
       <c r="P89">
-        <v>0.2496976972</v>
+        <v>0.248437336</v>
       </c>
       <c r="Q89">
-        <v>0.4276976971999999</v>
+        <v>0.426437336</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7963754010765867</v>
+        <v>0.8556224444633269</v>
       </c>
       <c r="T89">
-        <v>5.2333438670871</v>
+        <v>5.646440473645622</v>
       </c>
       <c r="U89">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V89">
         <v>0.3</v>
       </c>
       <c r="W89">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>9.853805271532648</v>
+        <v>9.432276728268699</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1356306933355992</v>
+        <v>0.1351510845312422</v>
       </c>
       <c r="C90">
-        <v>0.1286542979771489</v>
+        <v>0.119971913398103</v>
       </c>
       <c r="D90">
-        <v>0.3463742979771489</v>
+        <v>0.346631913398103</v>
       </c>
       <c r="E90">
-        <v>0.7567199999999999</v>
+        <v>0.76566</v>
       </c>
       <c r="F90">
-        <v>0.78672</v>
+        <v>0.79566</v>
       </c>
       <c r="G90">
         <v>0.569</v>
@@ -8649,28 +8649,28 @@
         <v>0.397</v>
       </c>
       <c r="M90">
-        <v>0.04208952</v>
+        <v>0.04256781</v>
       </c>
       <c r="N90">
-        <v>0.35491048</v>
+        <v>0.35443219</v>
       </c>
       <c r="O90">
-        <v>0.106473144</v>
+        <v>0.106329657</v>
       </c>
       <c r="P90">
-        <v>0.248437336</v>
+        <v>0.248102533</v>
       </c>
       <c r="Q90">
-        <v>0.426437336</v>
+        <v>0.426102533</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8556224444633269</v>
+        <v>0.9256416775567471</v>
       </c>
       <c r="T90">
-        <v>5.646440473645622</v>
+        <v>6.134645554123876</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>9.432276728268699</v>
+        <v>9.326296090872422</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1351510845312422</v>
+        <v>0.1346714757268851</v>
       </c>
       <c r="C91">
-        <v>0.119971913398103</v>
+        <v>0.1112899123065252</v>
       </c>
       <c r="D91">
-        <v>0.346631913398103</v>
+        <v>0.3468899123065252</v>
       </c>
       <c r="E91">
-        <v>0.76566</v>
+        <v>0.7746</v>
       </c>
       <c r="F91">
-        <v>0.79566</v>
+        <v>0.8046</v>
       </c>
       <c r="G91">
         <v>0.569</v>
@@ -8731,28 +8731,28 @@
         <v>0.397</v>
       </c>
       <c r="M91">
-        <v>0.04256781</v>
+        <v>0.0430461</v>
       </c>
       <c r="N91">
-        <v>0.35443219</v>
+        <v>0.3539539</v>
       </c>
       <c r="O91">
-        <v>0.106329657</v>
+        <v>0.10618617</v>
       </c>
       <c r="P91">
-        <v>0.248102533</v>
+        <v>0.24776773</v>
       </c>
       <c r="Q91">
-        <v>0.426102533</v>
+        <v>0.42576773</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9256416775567471</v>
+        <v>1.009664757268851</v>
       </c>
       <c r="T91">
-        <v>6.134645554123876</v>
+        <v>6.720491650697779</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>9.326296090872422</v>
+        <v>9.222670578751618</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1346714757268851</v>
+        <v>0.134191866922528</v>
       </c>
       <c r="C92">
-        <v>0.1112899123065252</v>
+        <v>0.1026082955593447</v>
       </c>
       <c r="D92">
-        <v>0.3468899123065252</v>
+        <v>0.3471482955593448</v>
       </c>
       <c r="E92">
-        <v>0.7746</v>
+        <v>0.78354</v>
       </c>
       <c r="F92">
-        <v>0.8046</v>
+        <v>0.81354</v>
       </c>
       <c r="G92">
         <v>0.569</v>
@@ -8813,28 +8813,28 @@
         <v>0.397</v>
       </c>
       <c r="M92">
-        <v>0.0430461</v>
+        <v>0.04352439</v>
       </c>
       <c r="N92">
-        <v>0.3539539</v>
+        <v>0.3534756099999999</v>
       </c>
       <c r="O92">
-        <v>0.10618617</v>
+        <v>0.106042683</v>
       </c>
       <c r="P92">
-        <v>0.24776773</v>
+        <v>0.247432927</v>
       </c>
       <c r="Q92">
-        <v>0.42576773</v>
+        <v>0.425432927</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.009664757268851</v>
+        <v>1.112359632472534</v>
       </c>
       <c r="T92">
-        <v>6.720491650697779</v>
+        <v>7.43652576873255</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>9.222670578751618</v>
+        <v>9.121322550413685</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.134191866922528</v>
+        <v>0.133712258118171</v>
       </c>
       <c r="C93">
-        <v>0.1026082955593447</v>
+        <v>0.09392706401604656</v>
       </c>
       <c r="D93">
-        <v>0.3471482955593448</v>
+        <v>0.3474070640160467</v>
       </c>
       <c r="E93">
-        <v>0.78354</v>
+        <v>0.7924800000000001</v>
       </c>
       <c r="F93">
-        <v>0.81354</v>
+        <v>0.8224800000000001</v>
       </c>
       <c r="G93">
         <v>0.569</v>
@@ -8895,28 +8895,28 @@
         <v>0.397</v>
       </c>
       <c r="M93">
-        <v>0.04352439</v>
+        <v>0.04400268</v>
       </c>
       <c r="N93">
-        <v>0.3534756099999999</v>
+        <v>0.3529973199999999</v>
       </c>
       <c r="O93">
-        <v>0.106042683</v>
+        <v>0.105899196</v>
       </c>
       <c r="P93">
-        <v>0.247432927</v>
+        <v>0.247098124</v>
       </c>
       <c r="Q93">
-        <v>0.425432927</v>
+        <v>0.425098124</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.112359632472534</v>
+        <v>1.240728226477138</v>
       </c>
       <c r="T93">
-        <v>7.43652576873255</v>
+        <v>8.331568416276017</v>
       </c>
       <c r="U93">
         <v>0.0535</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>9.121322550413685</v>
+        <v>9.022177740083102</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.133712258118171</v>
+        <v>0.1332326493138139</v>
       </c>
       <c r="C94">
-        <v>0.09392706401604656</v>
+        <v>0.08524621853867975</v>
       </c>
       <c r="D94">
-        <v>0.3474070640160467</v>
+        <v>0.3476662185386799</v>
       </c>
       <c r="E94">
-        <v>0.7924800000000001</v>
+        <v>0.80142</v>
       </c>
       <c r="F94">
-        <v>0.8224800000000001</v>
+        <v>0.83142</v>
       </c>
       <c r="G94">
         <v>0.569</v>
@@ -8977,28 +8977,28 @@
         <v>0.397</v>
       </c>
       <c r="M94">
-        <v>0.04400268</v>
+        <v>0.04448097</v>
       </c>
       <c r="N94">
-        <v>0.3529973199999999</v>
+        <v>0.35251903</v>
       </c>
       <c r="O94">
-        <v>0.105899196</v>
+        <v>0.105755709</v>
       </c>
       <c r="P94">
-        <v>0.247098124</v>
+        <v>0.246763321</v>
       </c>
       <c r="Q94">
-        <v>0.425098124</v>
+        <v>0.424763321</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.240728226477138</v>
+        <v>1.405773561625914</v>
       </c>
       <c r="T94">
-        <v>8.331568416276017</v>
+        <v>9.482337534546186</v>
       </c>
       <c r="U94">
         <v>0.0535</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>9.022177740083102</v>
+        <v>8.925165076211242</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1332326493138139</v>
+        <v>0.1327530405094569</v>
       </c>
       <c r="C95">
-        <v>0.08524621853867975</v>
+        <v>0.07656575999186777</v>
       </c>
       <c r="D95">
-        <v>0.3476662185386799</v>
+        <v>0.3479257599918679</v>
       </c>
       <c r="E95">
-        <v>0.80142</v>
+        <v>0.8103600000000001</v>
       </c>
       <c r="F95">
-        <v>0.83142</v>
+        <v>0.8403600000000001</v>
       </c>
       <c r="G95">
         <v>0.569</v>
@@ -9059,28 +9059,28 @@
         <v>0.397</v>
       </c>
       <c r="M95">
-        <v>0.04448097</v>
+        <v>0.04495926000000001</v>
       </c>
       <c r="N95">
-        <v>0.35251903</v>
+        <v>0.35204074</v>
       </c>
       <c r="O95">
-        <v>0.105755709</v>
+        <v>0.105612222</v>
       </c>
       <c r="P95">
-        <v>0.246763321</v>
+        <v>0.246428518</v>
       </c>
       <c r="Q95">
-        <v>0.424763321</v>
+        <v>0.424428518</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.405773561625914</v>
+        <v>1.625834008490949</v>
       </c>
       <c r="T95">
-        <v>9.482337534546186</v>
+        <v>11.01669635890641</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>8.925165076211242</v>
+        <v>8.830216511570695</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1327530405094569</v>
+        <v>0.1322734317050998</v>
       </c>
       <c r="C96">
-        <v>0.07656575999186777</v>
+        <v>0.06788568924281768</v>
       </c>
       <c r="D96">
-        <v>0.3479257599918679</v>
+        <v>0.3481856892428178</v>
       </c>
       <c r="E96">
-        <v>0.8103600000000001</v>
+        <v>0.8193</v>
       </c>
       <c r="F96">
-        <v>0.8403600000000001</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="G96">
         <v>0.569</v>
@@ -9141,28 +9141,28 @@
         <v>0.397</v>
       </c>
       <c r="M96">
-        <v>0.04495926000000001</v>
+        <v>0.04543755</v>
       </c>
       <c r="N96">
-        <v>0.35204074</v>
+        <v>0.35156245</v>
       </c>
       <c r="O96">
-        <v>0.105612222</v>
+        <v>0.105468735</v>
       </c>
       <c r="P96">
-        <v>0.246428518</v>
+        <v>0.246093715</v>
       </c>
       <c r="Q96">
-        <v>0.424428518</v>
+        <v>0.424093715</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.625834008490949</v>
+        <v>1.933918634101998</v>
       </c>
       <c r="T96">
-        <v>11.01669635890641</v>
+        <v>13.16479871301073</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>8.830216511570695</v>
+        <v>8.737266864080478</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1322734317050998</v>
+        <v>0.1317938229007427</v>
       </c>
       <c r="C97">
-        <v>0.06788568924281768</v>
+        <v>0.05920600716133007</v>
       </c>
       <c r="D97">
-        <v>0.3481856892428178</v>
+        <v>0.3484460071613302</v>
       </c>
       <c r="E97">
-        <v>0.8193</v>
+        <v>0.8282400000000001</v>
       </c>
       <c r="F97">
-        <v>0.8493000000000001</v>
+        <v>0.8582400000000001</v>
       </c>
       <c r="G97">
         <v>0.569</v>
@@ -9223,28 +9223,28 @@
         <v>0.397</v>
       </c>
       <c r="M97">
-        <v>0.04543755</v>
+        <v>0.04591584000000001</v>
       </c>
       <c r="N97">
-        <v>0.35156245</v>
+        <v>0.35108416</v>
       </c>
       <c r="O97">
-        <v>0.105468735</v>
+        <v>0.105325248</v>
       </c>
       <c r="P97">
-        <v>0.246093715</v>
+        <v>0.245758912</v>
       </c>
       <c r="Q97">
-        <v>0.424093715</v>
+        <v>0.423758912</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.933918634101998</v>
+        <v>2.396045572518573</v>
       </c>
       <c r="T97">
-        <v>13.16479871301073</v>
+        <v>16.38695224416722</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>8.737266864080478</v>
+        <v>8.646253667579639</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1317938229007427</v>
+        <v>0.1313142140963857</v>
       </c>
       <c r="C98">
-        <v>0.05920600716133018</v>
+        <v>0.05052671461980884</v>
       </c>
       <c r="D98">
-        <v>0.3484460071613302</v>
+        <v>0.3487067146198088</v>
       </c>
       <c r="E98">
-        <v>0.82824</v>
+        <v>0.8371799999999999</v>
       </c>
       <c r="F98">
-        <v>0.85824</v>
+        <v>0.86718</v>
       </c>
       <c r="G98">
         <v>0.569</v>
@@ -9305,28 +9305,28 @@
         <v>0.397</v>
       </c>
       <c r="M98">
-        <v>0.04591584</v>
+        <v>0.04639413</v>
       </c>
       <c r="N98">
-        <v>0.35108416</v>
+        <v>0.35060587</v>
       </c>
       <c r="O98">
-        <v>0.105325248</v>
+        <v>0.105181761</v>
       </c>
       <c r="P98">
-        <v>0.245758912</v>
+        <v>0.245424109</v>
       </c>
       <c r="Q98">
-        <v>0.423758912</v>
+        <v>0.423424109</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.396045572518566</v>
+        <v>3.166257136546187</v>
       </c>
       <c r="T98">
-        <v>16.38695224416717</v>
+        <v>21.75720812942795</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>8.646253667579641</v>
+        <v>8.557117031831398</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1313142140963857</v>
+        <v>0.1308346052920286</v>
       </c>
       <c r="C99">
-        <v>0.05052671461980884</v>
+        <v>0.04184781249327019</v>
       </c>
       <c r="D99">
-        <v>0.3487067146198088</v>
+        <v>0.3489678124932703</v>
       </c>
       <c r="E99">
-        <v>0.8371799999999999</v>
+        <v>0.84612</v>
       </c>
       <c r="F99">
-        <v>0.86718</v>
+        <v>0.87612</v>
       </c>
       <c r="G99">
         <v>0.569</v>
@@ -9387,28 +9387,28 @@
         <v>0.397</v>
       </c>
       <c r="M99">
-        <v>0.04639413</v>
+        <v>0.04687242</v>
       </c>
       <c r="N99">
-        <v>0.35060587</v>
+        <v>0.35012758</v>
       </c>
       <c r="O99">
-        <v>0.105181761</v>
+        <v>0.105038274</v>
       </c>
       <c r="P99">
-        <v>0.245424109</v>
+        <v>0.245089306</v>
       </c>
       <c r="Q99">
-        <v>0.423424109</v>
+        <v>0.423089306</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.166257136546187</v>
+        <v>4.706680264601427</v>
       </c>
       <c r="T99">
-        <v>21.75720812942795</v>
+        <v>32.4977198999495</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>8.557117031831398</v>
+        <v>8.469799511098424</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1308346052920286</v>
+        <v>0.1303549964876715</v>
       </c>
       <c r="C100">
-        <v>0.04184781249327019</v>
+        <v>0.03316930165935394</v>
       </c>
       <c r="D100">
-        <v>0.3489678124932703</v>
+        <v>0.3492293016593539</v>
       </c>
       <c r="E100">
-        <v>0.84612</v>
+        <v>0.8550599999999999</v>
       </c>
       <c r="F100">
-        <v>0.87612</v>
+        <v>0.88506</v>
       </c>
       <c r="G100">
         <v>0.569</v>
@@ -9469,28 +9469,28 @@
         <v>0.397</v>
       </c>
       <c r="M100">
-        <v>0.04687242</v>
+        <v>0.04735071</v>
       </c>
       <c r="N100">
-        <v>0.35012758</v>
+        <v>0.3496492899999999</v>
       </c>
       <c r="O100">
-        <v>0.105038274</v>
+        <v>0.104894787</v>
       </c>
       <c r="P100">
-        <v>0.245089306</v>
+        <v>0.244754503</v>
       </c>
       <c r="Q100">
-        <v>0.423089306</v>
+        <v>0.4227545029999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.706680264601427</v>
+        <v>9.327949648767147</v>
       </c>
       <c r="T100">
-        <v>32.4977198999495</v>
+        <v>64.71925521151417</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>8.469799511098424</v>
+        <v>8.384245980683289</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1303549964876715</v>
-      </c>
-      <c r="C101">
-        <v>0.03316930165935394</v>
-      </c>
-      <c r="D101">
-        <v>0.3492293016593539</v>
-      </c>
-      <c r="E101">
-        <v>0.8550599999999999</v>
-      </c>
-      <c r="F101">
-        <v>0.88506</v>
-      </c>
-      <c r="G101">
-        <v>0.569</v>
-      </c>
-      <c r="H101">
-        <v>0.864</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.575</v>
-      </c>
-      <c r="K101">
-        <v>0.178</v>
-      </c>
-      <c r="L101">
-        <v>0.397</v>
-      </c>
-      <c r="M101">
-        <v>0.04735071</v>
-      </c>
-      <c r="N101">
-        <v>0.3496492899999999</v>
-      </c>
-      <c r="O101">
-        <v>0.104894787</v>
-      </c>
-      <c r="P101">
-        <v>0.244754503</v>
-      </c>
-      <c r="Q101">
-        <v>0.4227545029999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.327949648767147</v>
-      </c>
-      <c r="T101">
-        <v>64.71925521151417</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03745</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>8.384245980683289</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
